--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080771A6-4E59-4C03-9475-CEE0DB5B19F9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD32CAA-B93C-4CA1-94C9-AD4F01D4292F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL" sheetId="1" r:id="rId1"/>
+    <sheet name="PLSQL" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PLSQL!$B$2:$G$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SQL!$B$3:$G$42</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="84">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -345,14 +347,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -688,16 +689,16 @@
       <c r="C3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>82</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -708,17 +709,17 @@
       <c r="C4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>29</v>
       </c>
       <c r="E4" s="3">
         <v>15</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <f>D4+E4</f>
         <v>44</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <f>F4/50</f>
         <v>0.88</v>
       </c>
@@ -730,17 +731,17 @@
       <c r="C5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <f t="shared" ref="F5:F42" si="0">D5+E5</f>
         <v>35</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <f t="shared" ref="G5:G42" si="1">F5/50</f>
         <v>0.7</v>
       </c>
@@ -752,17 +753,17 @@
       <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>17</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -774,17 +775,17 @@
       <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>14</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
@@ -796,17 +797,17 @@
       <c r="C8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>27</v>
       </c>
       <c r="E8" s="3">
         <v>14</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -818,17 +819,17 @@
       <c r="C9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>28</v>
       </c>
       <c r="E9" s="3">
         <v>19</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
@@ -840,17 +841,17 @@
       <c r="C10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>26</v>
       </c>
       <c r="E10" s="3">
         <v>15</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -862,17 +863,17 @@
       <c r="C11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>28</v>
       </c>
       <c r="E11" s="3">
         <v>16</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -884,17 +885,17 @@
       <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>28</v>
       </c>
       <c r="E12" s="3">
         <v>19</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
@@ -906,17 +907,17 @@
       <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>14</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -928,17 +929,17 @@
       <c r="C14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>24</v>
       </c>
       <c r="E14" s="3">
         <v>15</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
@@ -950,17 +951,17 @@
       <c r="C15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>26</v>
       </c>
       <c r="E15" s="3">
         <v>16</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
@@ -972,17 +973,17 @@
       <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>25</v>
       </c>
       <c r="E16" s="3">
         <v>13</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <f t="shared" si="1"/>
         <v>0.76</v>
       </c>
@@ -994,17 +995,17 @@
       <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>27</v>
       </c>
       <c r="E17" s="3">
         <v>18</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -1016,17 +1017,17 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>25</v>
       </c>
       <c r="E18" s="3">
         <v>15</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
@@ -1038,17 +1039,17 @@
       <c r="C19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>25</v>
       </c>
       <c r="E19" s="3">
         <v>16</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -1060,17 +1061,17 @@
       <c r="C20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>28</v>
       </c>
       <c r="E20" s="3">
         <v>16</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -1082,17 +1083,17 @@
       <c r="C21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>22</v>
       </c>
       <c r="E21" s="3">
         <v>16</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <f t="shared" si="1"/>
         <v>0.76</v>
       </c>
@@ -1104,17 +1105,17 @@
       <c r="C22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>28</v>
       </c>
       <c r="E22" s="3">
         <v>14</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
@@ -1126,17 +1127,17 @@
       <c r="C23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>28</v>
       </c>
       <c r="E23" s="3">
         <v>20</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
@@ -1148,17 +1149,17 @@
       <c r="C24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>29</v>
       </c>
       <c r="E24" s="3">
         <v>15</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -1170,17 +1171,17 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>21</v>
       </c>
       <c r="E25" s="3">
         <v>15</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <f t="shared" si="1"/>
         <v>0.72</v>
       </c>
@@ -1192,17 +1193,17 @@
       <c r="C26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>29</v>
       </c>
       <c r="E26" s="3">
         <v>12</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -1214,17 +1215,17 @@
       <c r="C27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>29</v>
       </c>
       <c r="E27" s="3">
         <v>20</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
@@ -1236,17 +1237,17 @@
       <c r="C28" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>27</v>
       </c>
       <c r="E28" s="3">
         <v>18</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -1258,17 +1259,17 @@
       <c r="C29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>28</v>
       </c>
       <c r="E29" s="3">
         <v>17</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -1280,17 +1281,17 @@
       <c r="C30" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>14</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
@@ -1302,17 +1303,17 @@
       <c r="C31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>28</v>
       </c>
       <c r="E31" s="3">
         <v>15</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
@@ -1324,17 +1325,17 @@
       <c r="C32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>27</v>
       </c>
       <c r="E32" s="3">
         <v>12</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
@@ -1346,17 +1347,17 @@
       <c r="C33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>29</v>
       </c>
       <c r="E33" s="3">
         <v>11</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
@@ -1368,17 +1369,17 @@
       <c r="C34" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>27</v>
       </c>
       <c r="E34" s="3">
         <v>17</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -1390,17 +1391,17 @@
       <c r="C35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>29</v>
       </c>
       <c r="E35" s="3">
         <v>17</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
@@ -1412,17 +1413,17 @@
       <c r="C36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>24</v>
       </c>
       <c r="E36" s="3">
         <v>19</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
@@ -1434,17 +1435,17 @@
       <c r="C37" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>28</v>
       </c>
       <c r="E37" s="3">
         <v>9</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <f t="shared" si="1"/>
         <v>0.74</v>
       </c>
@@ -1456,17 +1457,17 @@
       <c r="C38" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>28</v>
       </c>
       <c r="E38" s="3">
         <v>14</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
@@ -1478,17 +1479,17 @@
       <c r="C39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>30</v>
       </c>
       <c r="E39" s="3">
         <v>18</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
@@ -1500,17 +1501,17 @@
       <c r="C40" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>27</v>
       </c>
       <c r="E40" s="3">
         <v>12</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="4">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
@@ -1522,17 +1523,17 @@
       <c r="C41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>29</v>
       </c>
       <c r="E41" s="3">
         <v>16</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="4">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -1544,17 +1545,17 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>23</v>
       </c>
       <c r="E42" s="3">
         <v>14</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="4">
         <f t="shared" si="1"/>
         <v>0.74</v>
       </c>
@@ -1565,4 +1566,900 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D2B990-D605-47FE-B5DF-76FFF1700895}">
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3">
+        <f>D3+E3</f>
+        <v>43</v>
+      </c>
+      <c r="G3" s="4">
+        <f>F3/50</f>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F41" si="0">D4+E4</f>
+        <v>43</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" ref="G4:G41" si="1">F4/50</f>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="1"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3">
+        <v>17</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>18</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="1"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>17</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3">
+        <v>19</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="1"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" s="3">
+        <v>19</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="1"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>18</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>17</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>18</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>15</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>18</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G27" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29">
+        <v>27</v>
+      </c>
+      <c r="E29" s="3">
+        <v>18</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30">
+        <v>27</v>
+      </c>
+      <c r="E30" s="3">
+        <v>15</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>16</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3">
+        <v>14</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34">
+        <v>28</v>
+      </c>
+      <c r="E34" s="3">
+        <v>19</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="1"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>18</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36">
+        <v>27</v>
+      </c>
+      <c r="E36" s="3">
+        <v>18</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37">
+        <v>28</v>
+      </c>
+      <c r="E37" s="3">
+        <v>18</v>
+      </c>
+      <c r="F37" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="G37" s="4">
+        <f t="shared" si="1"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38">
+        <v>28</v>
+      </c>
+      <c r="E38" s="3">
+        <v>19</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="1"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39">
+        <v>28</v>
+      </c>
+      <c r="E39" s="3">
+        <v>15</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="G39" s="4">
+        <f t="shared" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40">
+        <v>27</v>
+      </c>
+      <c r="E40" s="3">
+        <v>19</v>
+      </c>
+      <c r="F40" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="1"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15</v>
+      </c>
+      <c r="F41" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD32CAA-B93C-4CA1-94C9-AD4F01D4292F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F4597B-9556-406A-B0C4-91252E03666B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
   <sheets>
-    <sheet name="SQL" sheetId="1" r:id="rId1"/>
-    <sheet name="PLSQL" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId1"/>
+    <sheet name="SQL" sheetId="1" r:id="rId2"/>
+    <sheet name="PLSQL" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PLSQL!$B$2:$G$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SQL!$B$3:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SQL!$B$3:$G$42</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="86">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -282,6 +283,12 @@
   </si>
   <si>
     <t>% (out of 100)</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>PL/SQL</t>
   </si>
 </sst>
 </file>
@@ -670,6 +677,623 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CBB81-7004-434A-99AB-007D8B0836DA}">
+  <dimension ref="B2:F41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.74</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F41" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB6A1EF-2DE7-4193-ADED-3E9C1E251A53}">
   <dimension ref="B3:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1568,7 +2192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D2B990-D605-47FE-B5DF-76FFF1700895}">
   <dimension ref="B2:G41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F4597B-9556-406A-B0C4-91252E03666B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B27E1E-F75A-4160-9E1D-0419F33A2DD1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="90">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -289,6 +289,18 @@
   </si>
   <si>
     <t>PL/SQL</t>
+  </si>
+  <si>
+    <t>570816</t>
+  </si>
+  <si>
+    <t>570838</t>
+  </si>
+  <si>
+    <t>Apeksha Prabhakar Shetty</t>
+  </si>
+  <si>
+    <t>Harshitha B H</t>
   </si>
 </sst>
 </file>
@@ -354,7 +366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -363,6 +375,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1295,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB6A1EF-2DE7-4193-ADED-3E9C1E251A53}">
-  <dimension ref="B3:G42"/>
+  <dimension ref="B3:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -1362,11 +1376,11 @@
         <v>10</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F42" si="0">D5+E5</f>
+        <f t="shared" ref="F5:F44" si="0">D5+E5</f>
         <v>35</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" ref="G5:G42" si="1">F5/50</f>
+        <f t="shared" ref="G5:G44" si="1">F5/50</f>
         <v>0.7</v>
       </c>
     </row>
@@ -2182,6 +2196,50 @@
       <c r="G42" s="4">
         <f t="shared" si="1"/>
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="6">
+        <v>27</v>
+      </c>
+      <c r="E43" s="6">
+        <v>17</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="6">
+        <v>28</v>
+      </c>
+      <c r="E44" s="6">
+        <v>13</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>

--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B27E1E-F75A-4160-9E1D-0419F33A2DD1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD92C3-E778-4813-9299-C2AC71A18270}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="90">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -338,7 +338,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -361,12 +361,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -375,8 +388,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2205,17 +2221,17 @@
       <c r="C43" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="3">
         <v>27</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="3">
         <v>17</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="6">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
@@ -2227,17 +2243,17 @@
       <c r="C44" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="3">
         <v>28</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="3">
         <v>13</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="6">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -2252,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D2B990-D605-47FE-B5DF-76FFF1700895}">
-  <dimension ref="B2:G41"/>
+  <dimension ref="B2:G43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -2319,11 +2335,11 @@
         <v>16</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" ref="F4:F41" si="0">D4+E4</f>
+        <f t="shared" ref="F4:F43" si="0">D4+E4</f>
         <v>43</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" ref="G4:G41" si="1">F4/50</f>
+        <f t="shared" ref="G4:G43" si="1">F4/50</f>
         <v>0.86</v>
       </c>
     </row>
@@ -3120,23 +3136,67 @@
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D41">
         <v>27</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="8">
         <v>15</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="8">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="9">
+        <f t="shared" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="3">
+        <v>26</v>
+      </c>
+      <c r="E42" s="10">
+        <v>15</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="G42" s="6">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3">
+        <v>27</v>
+      </c>
+      <c r="E43" s="10">
+        <v>15</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G43" s="6">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>

--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD92C3-E778-4813-9299-C2AC71A18270}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B33A71-1251-47A6-BCB4-C2FE2A670F3E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -379,7 +379,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -392,7 +392,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3167,10 +3166,10 @@
       <c r="D42" s="3">
         <v>26</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="3">
         <v>15</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -3189,10 +3188,10 @@
       <c r="D43" s="3">
         <v>27</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="3">
         <v>15</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>

--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B33A71-1251-47A6-BCB4-C2FE2A670F3E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2E440B-62D7-4F8C-9B63-764390A84079}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
     <sheet name="SQL" sheetId="1" r:id="rId2"/>
     <sheet name="PLSQL" sheetId="2" r:id="rId3"/>
+    <sheet name="Java" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SQL!$B$3:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$B$2:$F$43</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="103">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -301,13 +303,52 @@
   </si>
   <si>
     <t>Harshitha B H</t>
+  </si>
+  <si>
+    <t>Srinivas M</t>
+  </si>
+  <si>
+    <t>Adithya M Murthy</t>
+  </si>
+  <si>
+    <t>Aditya Harivalad</t>
+  </si>
+  <si>
+    <t>omkar Rampure</t>
+  </si>
+  <si>
+    <t>Rekha S</t>
+  </si>
+  <si>
+    <t>Monisha J</t>
+  </si>
+  <si>
+    <t>MCQ (out of 30)</t>
+  </si>
+  <si>
+    <t>Coding (out of 20)</t>
+  </si>
+  <si>
+    <t>Total for 50</t>
+  </si>
+  <si>
+    <t>Total (100)</t>
+  </si>
+  <si>
+    <t>Emp ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Java</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +366,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -379,7 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -392,6 +441,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,17 +758,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CBB81-7004-434A-99AB-007D8B0836DA}">
-  <dimension ref="B2:F41"/>
+  <dimension ref="B2:G43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="10" customWidth="1"/>
+    <col min="7" max="7" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -730,9 +782,12 @@
       <c r="E2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
@@ -745,9 +800,12 @@
       <c r="E3" s="4">
         <v>0.86</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
@@ -760,9 +818,12 @@
       <c r="E4" s="4">
         <v>0.86</v>
       </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
@@ -775,9 +836,12 @@
       <c r="E5" s="4">
         <v>0.86</v>
       </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
@@ -790,9 +854,12 @@
       <c r="E6" s="4">
         <v>0.84</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -805,9 +872,12 @@
       <c r="E7" s="4">
         <v>0.88</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -820,9 +890,12 @@
       <c r="E8" s="4">
         <v>0.84</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -835,9 +908,12 @@
       <c r="E9" s="4">
         <v>0.9</v>
       </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -850,9 +926,12 @@
       <c r="E10" s="4">
         <v>0.92</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -865,9 +944,12 @@
       <c r="E11" s="4">
         <v>0.9</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -880,9 +962,12 @@
       <c r="E12" s="4">
         <v>0.9</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -895,9 +980,12 @@
       <c r="E13" s="4">
         <v>0.9</v>
       </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -910,9 +998,12 @@
       <c r="E14" s="4">
         <v>0.88</v>
       </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
@@ -925,9 +1016,12 @@
       <c r="E15" s="4">
         <v>0.94</v>
       </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -940,9 +1034,12 @@
       <c r="E16" s="4">
         <v>0.86</v>
       </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F16" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -955,9 +1052,12 @@
       <c r="E17" s="4">
         <v>0.86</v>
       </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
@@ -970,9 +1070,12 @@
       <c r="E18" s="4">
         <v>0.82</v>
       </c>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
@@ -985,9 +1088,12 @@
       <c r="E19" s="4">
         <v>0.98</v>
       </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1000,9 +1106,12 @@
       <c r="E20" s="4">
         <v>0.86</v>
       </c>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1015,9 +1124,12 @@
       <c r="E21" s="4">
         <v>0.98</v>
       </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1030,9 +1142,12 @@
       <c r="E22" s="4">
         <v>0.88</v>
       </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1045,9 +1160,12 @@
       <c r="E23" s="4">
         <v>0.88</v>
       </c>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1060,9 +1178,12 @@
       <c r="E24" s="4">
         <v>0.86</v>
       </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1075,9 +1196,12 @@
       <c r="E25" s="4">
         <v>0.9</v>
       </c>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
@@ -1090,9 +1214,12 @@
       <c r="E26" s="4">
         <v>0.8</v>
       </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F26" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1105,9 +1232,12 @@
       <c r="E27" s="4">
         <v>0.9</v>
       </c>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
@@ -1120,9 +1250,12 @@
       <c r="E28" s="4">
         <v>0.9</v>
       </c>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1135,9 +1268,12 @@
       <c r="E29" s="4">
         <v>0.9</v>
       </c>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
@@ -1150,9 +1286,12 @@
       <c r="E30" s="4">
         <v>0.84</v>
       </c>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F30" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
@@ -1165,9 +1304,12 @@
       <c r="E31" s="4">
         <v>0.84</v>
       </c>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F31" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>23</v>
       </c>
@@ -1180,9 +1322,12 @@
       <c r="E32" s="4">
         <v>0.86</v>
       </c>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
@@ -1195,9 +1340,12 @@
       <c r="E33" s="4">
         <v>0.88</v>
       </c>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F33" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
@@ -1210,9 +1358,12 @@
       <c r="E34" s="4">
         <v>0.94</v>
       </c>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
@@ -1225,9 +1376,12 @@
       <c r="E35" s="4">
         <v>0.9</v>
       </c>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
@@ -1240,9 +1394,12 @@
       <c r="E36" s="4">
         <v>0.9</v>
       </c>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>17</v>
       </c>
@@ -1255,9 +1412,12 @@
       <c r="E37" s="4">
         <v>0.92</v>
       </c>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1270,9 +1430,12 @@
       <c r="E38" s="4">
         <v>0.94</v>
       </c>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>20</v>
       </c>
@@ -1285,9 +1448,12 @@
       <c r="E39" s="4">
         <v>0.86</v>
       </c>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
@@ -1300,9 +1466,12 @@
       <c r="E40" s="4">
         <v>0.92</v>
       </c>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
@@ -1315,7 +1484,46 @@
       <c r="E41" s="4">
         <v>0.84</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.82</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="G43" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3203,4 +3411,948 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCAF52D-6C58-4CC2-BF95-73A4DEB8C0BA}">
+  <dimension ref="B2:G43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="3">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3">
+        <f>D3+E3</f>
+        <v>47</v>
+      </c>
+      <c r="G3" s="4">
+        <f>F3/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="3">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3">
+        <f>D4+E4</f>
+        <v>44</v>
+      </c>
+      <c r="G4" s="4">
+        <f>F4/50</f>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="3">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3">
+        <f>D5+E5</f>
+        <v>48</v>
+      </c>
+      <c r="G5" s="4">
+        <f>F5/50</f>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="3">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3">
+        <f>D6+E6</f>
+        <v>44</v>
+      </c>
+      <c r="G6" s="4">
+        <f>F6/50</f>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="3">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3">
+        <f>D7+E7</f>
+        <v>49</v>
+      </c>
+      <c r="G7" s="4">
+        <f>F7/50</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3">
+        <f>D8+E8</f>
+        <v>42</v>
+      </c>
+      <c r="G8" s="4">
+        <f>F8/50</f>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="3">
+        <v>29</v>
+      </c>
+      <c r="E9" s="3">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3">
+        <f>D9+E9</f>
+        <v>48</v>
+      </c>
+      <c r="G9" s="4">
+        <f>F9/50</f>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3">
+        <v>18</v>
+      </c>
+      <c r="F10" s="3">
+        <f>D10+E10</f>
+        <v>46</v>
+      </c>
+      <c r="G10" s="4">
+        <f>F10/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3">
+        <f>D11+E11</f>
+        <v>42</v>
+      </c>
+      <c r="G11" s="4">
+        <f>F11/50</f>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3">
+        <f>D12+E12</f>
+        <v>45</v>
+      </c>
+      <c r="G12" s="4">
+        <f>F12/50</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="3">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3">
+        <v>20</v>
+      </c>
+      <c r="F13" s="3">
+        <f>D13+E13</f>
+        <v>49</v>
+      </c>
+      <c r="G13" s="4">
+        <f>F13/50</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="3">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3">
+        <v>17</v>
+      </c>
+      <c r="F14" s="3">
+        <f>D14+E14</f>
+        <v>45</v>
+      </c>
+      <c r="G14" s="4">
+        <f>F14/50</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3">
+        <v>29</v>
+      </c>
+      <c r="E15" s="3">
+        <v>17</v>
+      </c>
+      <c r="F15" s="3">
+        <f>D15+E15</f>
+        <v>46</v>
+      </c>
+      <c r="G15" s="4">
+        <f>F15/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="3">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3">
+        <v>19</v>
+      </c>
+      <c r="F16" s="3">
+        <f>D16+E16</f>
+        <v>46</v>
+      </c>
+      <c r="G16" s="4">
+        <f>F16/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="3">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>19</v>
+      </c>
+      <c r="F17" s="3">
+        <f>D17+E17</f>
+        <v>44</v>
+      </c>
+      <c r="G17" s="4">
+        <f>F17/50</f>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="3">
+        <v>29</v>
+      </c>
+      <c r="E18" s="3">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3">
+        <f>D18+E18</f>
+        <v>49</v>
+      </c>
+      <c r="G18" s="4">
+        <f>F18/50</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="3">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>15</v>
+      </c>
+      <c r="F19" s="3">
+        <f>D19+E19</f>
+        <v>41</v>
+      </c>
+      <c r="G19" s="4">
+        <f>F19/50</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="3">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3">
+        <f>D20+E20</f>
+        <v>43</v>
+      </c>
+      <c r="G20" s="4">
+        <f>F20/50</f>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>14</v>
+      </c>
+      <c r="F21" s="3">
+        <f>D21+E21</f>
+        <v>41</v>
+      </c>
+      <c r="G21" s="4">
+        <f>F21/50</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3">
+        <f>D22+E22</f>
+        <v>40</v>
+      </c>
+      <c r="G22" s="4">
+        <f>F22/50</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="3">
+        <v>28</v>
+      </c>
+      <c r="E23" s="3">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3">
+        <f>D23+E23</f>
+        <v>47</v>
+      </c>
+      <c r="G23" s="4">
+        <f>F23/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="3">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3">
+        <f>D24+E24</f>
+        <v>42</v>
+      </c>
+      <c r="G24" s="4">
+        <f>F24/50</f>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="3">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>14</v>
+      </c>
+      <c r="F25" s="3">
+        <f>D25+E25</f>
+        <v>41</v>
+      </c>
+      <c r="G25" s="4">
+        <f>F25/50</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="3">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>16</v>
+      </c>
+      <c r="F26" s="3">
+        <f>D26+E26</f>
+        <v>43</v>
+      </c>
+      <c r="G26" s="4">
+        <f>F26/50</f>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="3">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3">
+        <v>17</v>
+      </c>
+      <c r="F27" s="3">
+        <f>D27+E27</f>
+        <v>45</v>
+      </c>
+      <c r="G27" s="4">
+        <f>F27/50</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3">
+        <f>D28+E28</f>
+        <v>46</v>
+      </c>
+      <c r="G28" s="4">
+        <f>F28/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="3">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>20</v>
+      </c>
+      <c r="F29" s="3">
+        <f>D29+E29</f>
+        <v>46</v>
+      </c>
+      <c r="G29" s="4">
+        <f>F29/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3">
+        <v>16</v>
+      </c>
+      <c r="F30" s="3">
+        <f>D30+E30</f>
+        <v>45</v>
+      </c>
+      <c r="G30" s="4">
+        <f>F30/50</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3">
+        <v>19</v>
+      </c>
+      <c r="F31" s="3">
+        <f>D31+E31</f>
+        <v>49</v>
+      </c>
+      <c r="G31" s="4">
+        <f>F31/50</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="3">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3">
+        <f>D32+E32</f>
+        <v>42</v>
+      </c>
+      <c r="G32" s="4">
+        <f>F32/50</f>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="3">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3">
+        <f>D33+E33</f>
+        <v>48</v>
+      </c>
+      <c r="G33" s="4">
+        <f>F33/50</f>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="3">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3">
+        <v>19</v>
+      </c>
+      <c r="F34" s="3">
+        <f>D34+E34</f>
+        <v>46</v>
+      </c>
+      <c r="G34" s="4">
+        <f>F34/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="3">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3">
+        <f>D35+E35</f>
+        <v>47</v>
+      </c>
+      <c r="G35" s="4">
+        <f>F35/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="3">
+        <v>28</v>
+      </c>
+      <c r="E36" s="3">
+        <v>18</v>
+      </c>
+      <c r="F36" s="3">
+        <f>D36+E36</f>
+        <v>46</v>
+      </c>
+      <c r="G36" s="4">
+        <f>F36/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="3">
+        <v>28</v>
+      </c>
+      <c r="E37" s="3">
+        <v>19</v>
+      </c>
+      <c r="F37" s="3">
+        <f>D37+E37</f>
+        <v>47</v>
+      </c>
+      <c r="G37" s="4">
+        <f>F37/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="3">
+        <v>29</v>
+      </c>
+      <c r="E38" s="3">
+        <v>19</v>
+      </c>
+      <c r="F38" s="3">
+        <f>D38+E38</f>
+        <v>48</v>
+      </c>
+      <c r="G38" s="4">
+        <f>F38/50</f>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="3">
+        <v>27</v>
+      </c>
+      <c r="E39" s="3">
+        <v>18</v>
+      </c>
+      <c r="F39" s="3">
+        <f>D39+E39</f>
+        <v>45</v>
+      </c>
+      <c r="G39" s="4">
+        <f>F39/50</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="3">
+        <v>28</v>
+      </c>
+      <c r="E40" s="3">
+        <v>19</v>
+      </c>
+      <c r="F40" s="3">
+        <f>D40+E40</f>
+        <v>47</v>
+      </c>
+      <c r="G40" s="4">
+        <f>F40/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="3">
+        <v>29</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20</v>
+      </c>
+      <c r="F41" s="3">
+        <f>D41+E41</f>
+        <v>49</v>
+      </c>
+      <c r="G41" s="4">
+        <f>F41/50</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="3">
+        <v>28</v>
+      </c>
+      <c r="E42" s="3">
+        <v>19</v>
+      </c>
+      <c r="F42" s="3">
+        <f>D42+E42</f>
+        <v>47</v>
+      </c>
+      <c r="G42" s="4">
+        <f>F42/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16</v>
+      </c>
+      <c r="F43" s="3">
+        <f>D43+E43</f>
+        <v>42</v>
+      </c>
+      <c r="G43" s="4">
+        <f>F43/50</f>
+        <v>0.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G43">
+    <sortCondition ref="B3:B43"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2E440B-62D7-4F8C-9B63-764390A84079}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C4B216-67FA-4FCF-8DDE-01EDC96B59F8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="SQL" sheetId="1" r:id="rId2"/>
     <sheet name="PLSQL" sheetId="2" r:id="rId3"/>
     <sheet name="Java" sheetId="4" r:id="rId4"/>
+    <sheet name="Spring" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="128">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -342,6 +343,81 @@
   </si>
   <si>
     <t>Java</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>Learner Name</t>
+  </si>
+  <si>
+    <t>Learner Email</t>
+  </si>
+  <si>
+    <t>Submitted At</t>
+  </si>
+  <si>
+    <t>MCQ Score</t>
+  </si>
+  <si>
+    <t>Max MCQ Score</t>
+  </si>
+  <si>
+    <t>Coding Score</t>
+  </si>
+  <si>
+    <t>Max Coding Score</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>MCQ for 30</t>
+  </si>
+  <si>
+    <t>Coding for 20</t>
+  </si>
+  <si>
+    <t>for 50</t>
+  </si>
+  <si>
+    <t>for 100</t>
+  </si>
+  <si>
+    <t>finalized</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atharv </t>
+  </si>
+  <si>
+    <t>Hari prasad</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Yashwanth M</t>
+  </si>
+  <si>
+    <t>GUNJAN  MAHAJAN</t>
+  </si>
+  <si>
+    <t>Ashritha</t>
+  </si>
+  <si>
+    <t>omkar</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>570378</t>
+  </si>
+  <si>
+    <t>570426</t>
   </si>
 </sst>
 </file>
@@ -428,7 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -441,8 +517,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,18 +836,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CBB81-7004-434A-99AB-007D8B0836DA}">
-  <dimension ref="B2:G43"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.88671875" customWidth="1"/>
+    <col min="8" max="8" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,9 +863,12 @@
       <c r="F2" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
@@ -803,9 +884,12 @@
       <c r="F3" s="4">
         <v>0.94</v>
       </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G3" s="4">
+        <v>0.91599999999999993</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
@@ -821,9 +905,12 @@
       <c r="F4" s="4">
         <v>0.88</v>
       </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="4">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
@@ -839,9 +926,12 @@
       <c r="F5" s="4">
         <v>0.96</v>
       </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="4">
+        <v>0.90799999999999992</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
@@ -857,9 +947,12 @@
       <c r="F6" s="4">
         <v>0.88</v>
       </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="4">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -875,9 +968,12 @@
       <c r="F7" s="4">
         <v>0.98</v>
       </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="4">
+        <v>0.90799999999999992</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -893,9 +989,12 @@
       <c r="F8" s="4">
         <v>0.84</v>
       </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="4">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -911,9 +1010,12 @@
       <c r="F9" s="4">
         <v>0.96</v>
       </c>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -929,9 +1031,12 @@
       <c r="F10" s="4">
         <v>0.92</v>
       </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -947,9 +1052,12 @@
       <c r="F11" s="4">
         <v>0.84</v>
       </c>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="4">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -965,9 +1073,12 @@
       <c r="F12" s="4">
         <v>0.9</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="4">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -983,9 +1094,12 @@
       <c r="F13" s="4">
         <v>0.98</v>
       </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G13" s="4">
+        <v>0.89</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1001,9 +1115,12 @@
       <c r="F14" s="4">
         <v>0.9</v>
       </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G14" s="4">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1019,9 +1136,12 @@
       <c r="F15" s="4">
         <v>0.92</v>
       </c>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1037,9 +1157,12 @@
       <c r="F16" s="4">
         <v>0.92</v>
       </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G16" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -1055,9 +1178,12 @@
       <c r="F17" s="4">
         <v>0.88</v>
       </c>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="4">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1073,9 +1199,12 @@
       <c r="F18" s="4">
         <v>0.98</v>
       </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G18" s="4">
+        <v>0.90199999999999991</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1091,9 +1220,12 @@
       <c r="F19" s="4">
         <v>0.82</v>
       </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G19" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1109,9 +1241,12 @@
       <c r="F20" s="4">
         <v>0.86</v>
       </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="4">
+        <v>0.83200000000000007</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1127,9 +1262,12 @@
       <c r="F21" s="4">
         <v>0.82</v>
       </c>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1145,9 +1283,12 @@
       <c r="F22" s="4">
         <v>0.8</v>
       </c>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="4">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1163,9 +1304,12 @@
       <c r="F23" s="4">
         <v>0.94</v>
       </c>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="4">
+        <v>0.872</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1181,9 +1325,12 @@
       <c r="F24" s="4">
         <v>0.84</v>
       </c>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G24" s="4">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1199,9 +1346,12 @@
       <c r="F25" s="4">
         <v>0.82</v>
       </c>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="4">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
@@ -1217,9 +1367,12 @@
       <c r="F26" s="4">
         <v>0.86</v>
       </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="4">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1235,9 +1388,12 @@
       <c r="F27" s="4">
         <v>0.9</v>
       </c>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
@@ -1253,9 +1409,12 @@
       <c r="F28" s="4">
         <v>0.92</v>
       </c>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="4">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1271,9 +1430,12 @@
       <c r="F29" s="4">
         <v>0.92</v>
       </c>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
@@ -1289,9 +1451,12 @@
       <c r="F30" s="4">
         <v>0.9</v>
       </c>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="4">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
@@ -1307,9 +1472,12 @@
       <c r="F31" s="4">
         <v>0.98</v>
       </c>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G31" s="4">
+        <v>0.87599999999999989</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>23</v>
       </c>
@@ -1325,9 +1493,12 @@
       <c r="F32" s="4">
         <v>0.84</v>
       </c>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G32" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
@@ -1343,9 +1514,12 @@
       <c r="F33" s="4">
         <v>0.96</v>
       </c>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="4">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
@@ -1361,9 +1535,12 @@
       <c r="F34" s="4">
         <v>0.92</v>
       </c>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G34" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
@@ -1379,9 +1556,12 @@
       <c r="F35" s="4">
         <v>0.94</v>
       </c>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G35" s="4">
+        <v>0.93599999999999994</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
@@ -1397,9 +1577,12 @@
       <c r="F36" s="4">
         <v>0.92</v>
       </c>
-      <c r="G36" s="3"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G36" s="4">
+        <v>0.87599999999999989</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>17</v>
       </c>
@@ -1415,9 +1598,12 @@
       <c r="F37" s="4">
         <v>0.94</v>
       </c>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G37" s="4">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1433,9 +1619,12 @@
       <c r="F38" s="4">
         <v>0.96</v>
       </c>
-      <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G38" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>20</v>
       </c>
@@ -1451,9 +1640,12 @@
       <c r="F39" s="4">
         <v>0.9</v>
       </c>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G39" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
@@ -1469,9 +1661,12 @@
       <c r="F40" s="4">
         <v>0.94</v>
       </c>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G40" s="4">
+        <v>0.82400000000000007</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
@@ -1487,9 +1682,12 @@
       <c r="F41" s="4">
         <v>0.98</v>
       </c>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G41" s="4">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>86</v>
       </c>
@@ -1505,9 +1703,12 @@
       <c r="F42" s="4">
         <v>0.94</v>
       </c>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G42" s="4">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>87</v>
       </c>
@@ -1523,7 +1724,10 @@
       <c r="F43" s="4">
         <v>0.84</v>
       </c>
-      <c r="G43" s="3"/>
+      <c r="G43" s="4">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="H43" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3427,22 +3631,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3460,11 +3664,11 @@
         <v>20</v>
       </c>
       <c r="F3" s="3">
-        <f>D3+E3</f>
+        <f t="shared" ref="F3:F43" si="0">D3+E3</f>
         <v>47</v>
       </c>
       <c r="G3" s="4">
-        <f>F3/50</f>
+        <f t="shared" ref="G3:G43" si="1">F3/50</f>
         <v>0.94</v>
       </c>
     </row>
@@ -3482,11 +3686,11 @@
         <v>16</v>
       </c>
       <c r="F4" s="3">
-        <f>D4+E4</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="G4" s="4">
-        <f>F4/50</f>
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
     </row>
@@ -3504,11 +3708,11 @@
         <v>20</v>
       </c>
       <c r="F5" s="3">
-        <f>D5+E5</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="G5" s="4">
-        <f>F5/50</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
     </row>
@@ -3526,11 +3730,11 @@
         <v>19</v>
       </c>
       <c r="F6" s="3">
-        <f>D6+E6</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="G6" s="4">
-        <f>F6/50</f>
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
     </row>
@@ -3548,11 +3752,11 @@
         <v>20</v>
       </c>
       <c r="F7" s="3">
-        <f>D7+E7</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G7" s="4">
-        <f>F7/50</f>
+        <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
     </row>
@@ -3570,11 +3774,11 @@
         <v>16</v>
       </c>
       <c r="F8" s="3">
-        <f>D8+E8</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="G8" s="4">
-        <f>F8/50</f>
+        <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
     </row>
@@ -3592,11 +3796,11 @@
         <v>19</v>
       </c>
       <c r="F9" s="3">
-        <f>D9+E9</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="G9" s="4">
-        <f>F9/50</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
     </row>
@@ -3614,11 +3818,11 @@
         <v>18</v>
       </c>
       <c r="F10" s="3">
-        <f>D10+E10</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G10" s="4">
-        <f>F10/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -3636,11 +3840,11 @@
         <v>17</v>
       </c>
       <c r="F11" s="3">
-        <f>D11+E11</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="G11" s="4">
-        <f>F11/50</f>
+        <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
     </row>
@@ -3658,11 +3862,11 @@
         <v>17</v>
       </c>
       <c r="F12" s="3">
-        <f>D12+E12</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G12" s="4">
-        <f>F12/50</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3680,11 +3884,11 @@
         <v>20</v>
       </c>
       <c r="F13" s="3">
-        <f>D13+E13</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G13" s="4">
-        <f>F13/50</f>
+        <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
     </row>
@@ -3702,11 +3906,11 @@
         <v>17</v>
       </c>
       <c r="F14" s="3">
-        <f>D14+E14</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G14" s="4">
-        <f>F14/50</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3724,11 +3928,11 @@
         <v>17</v>
       </c>
       <c r="F15" s="3">
-        <f>D15+E15</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G15" s="4">
-        <f>F15/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -3746,11 +3950,11 @@
         <v>19</v>
       </c>
       <c r="F16" s="3">
-        <f>D16+E16</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G16" s="4">
-        <f>F16/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -3768,11 +3972,11 @@
         <v>19</v>
       </c>
       <c r="F17" s="3">
-        <f>D17+E17</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="G17" s="4">
-        <f>F17/50</f>
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
     </row>
@@ -3790,11 +3994,11 @@
         <v>20</v>
       </c>
       <c r="F18" s="3">
-        <f>D18+E18</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G18" s="4">
-        <f>F18/50</f>
+        <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
     </row>
@@ -3812,11 +4016,11 @@
         <v>15</v>
       </c>
       <c r="F19" s="3">
-        <f>D19+E19</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="G19" s="4">
-        <f>F19/50</f>
+        <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
     </row>
@@ -3834,11 +4038,11 @@
         <v>17</v>
       </c>
       <c r="F20" s="3">
-        <f>D20+E20</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="G20" s="4">
-        <f>F20/50</f>
+        <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
     </row>
@@ -3856,11 +4060,11 @@
         <v>14</v>
       </c>
       <c r="F21" s="3">
-        <f>D21+E21</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="G21" s="4">
-        <f>F21/50</f>
+        <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
     </row>
@@ -3878,11 +4082,11 @@
         <v>13</v>
       </c>
       <c r="F22" s="3">
-        <f>D22+E22</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="G22" s="4">
-        <f>F22/50</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -3900,11 +4104,11 @@
         <v>19</v>
       </c>
       <c r="F23" s="3">
-        <f>D23+E23</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="G23" s="4">
-        <f>F23/50</f>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
     </row>
@@ -3922,11 +4126,11 @@
         <v>17</v>
       </c>
       <c r="F24" s="3">
-        <f>D24+E24</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="G24" s="4">
-        <f>F24/50</f>
+        <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
     </row>
@@ -3944,11 +4148,11 @@
         <v>14</v>
       </c>
       <c r="F25" s="3">
-        <f>D25+E25</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="G25" s="4">
-        <f>F25/50</f>
+        <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
     </row>
@@ -3966,11 +4170,11 @@
         <v>16</v>
       </c>
       <c r="F26" s="3">
-        <f>D26+E26</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="G26" s="4">
-        <f>F26/50</f>
+        <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
     </row>
@@ -3988,11 +4192,11 @@
         <v>17</v>
       </c>
       <c r="F27" s="3">
-        <f>D27+E27</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G27" s="4">
-        <f>F27/50</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -4010,11 +4214,11 @@
         <v>20</v>
       </c>
       <c r="F28" s="3">
-        <f>D28+E28</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G28" s="4">
-        <f>F28/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -4032,11 +4236,11 @@
         <v>20</v>
       </c>
       <c r="F29" s="3">
-        <f>D29+E29</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G29" s="4">
-        <f>F29/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -4054,11 +4258,11 @@
         <v>16</v>
       </c>
       <c r="F30" s="3">
-        <f>D30+E30</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G30" s="4">
-        <f>F30/50</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -4076,11 +4280,11 @@
         <v>19</v>
       </c>
       <c r="F31" s="3">
-        <f>D31+E31</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G31" s="4">
-        <f>F31/50</f>
+        <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
     </row>
@@ -4098,11 +4302,11 @@
         <v>17</v>
       </c>
       <c r="F32" s="3">
-        <f>D32+E32</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="G32" s="4">
-        <f>F32/50</f>
+        <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
     </row>
@@ -4120,11 +4324,11 @@
         <v>20</v>
       </c>
       <c r="F33" s="3">
-        <f>D33+E33</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="G33" s="4">
-        <f>F33/50</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
     </row>
@@ -4142,11 +4346,11 @@
         <v>19</v>
       </c>
       <c r="F34" s="3">
-        <f>D34+E34</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G34" s="4">
-        <f>F34/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -4164,11 +4368,11 @@
         <v>20</v>
       </c>
       <c r="F35" s="3">
-        <f>D35+E35</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="G35" s="4">
-        <f>F35/50</f>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
     </row>
@@ -4186,11 +4390,11 @@
         <v>18</v>
       </c>
       <c r="F36" s="3">
-        <f>D36+E36</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="G36" s="4">
-        <f>F36/50</f>
+        <f t="shared" si="1"/>
         <v>0.92</v>
       </c>
     </row>
@@ -4208,11 +4412,11 @@
         <v>19</v>
       </c>
       <c r="F37" s="3">
-        <f>D37+E37</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="G37" s="4">
-        <f>F37/50</f>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
     </row>
@@ -4230,11 +4434,11 @@
         <v>19</v>
       </c>
       <c r="F38" s="3">
-        <f>D38+E38</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="G38" s="4">
-        <f>F38/50</f>
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
     </row>
@@ -4252,11 +4456,11 @@
         <v>18</v>
       </c>
       <c r="F39" s="3">
-        <f>D39+E39</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G39" s="4">
-        <f>F39/50</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -4274,11 +4478,11 @@
         <v>19</v>
       </c>
       <c r="F40" s="3">
-        <f>D40+E40</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="G40" s="4">
-        <f>F40/50</f>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
     </row>
@@ -4296,11 +4500,11 @@
         <v>20</v>
       </c>
       <c r="F41" s="3">
-        <f>D41+E41</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G41" s="4">
-        <f>F41/50</f>
+        <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
     </row>
@@ -4318,11 +4522,11 @@
         <v>19</v>
       </c>
       <c r="F42" s="3">
-        <f>D42+E42</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="G42" s="4">
-        <f>F42/50</f>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
     </row>
@@ -4340,11 +4544,11 @@
         <v>16</v>
       </c>
       <c r="F43" s="3">
-        <f>D43+E43</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="G43" s="4">
-        <f>F43/50</f>
+        <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
     </row>
@@ -4355,4 +4559,2174 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3184FB6D-2A70-4EF3-B492-47CDD15B49E8}">
+  <dimension ref="A1:S42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" customWidth="1"/>
+    <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2">
+        <v>90.8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>570362</v>
+      </c>
+      <c r="I2" s="12">
+        <v>45901.613923611112</v>
+      </c>
+      <c r="J2" s="13">
+        <v>29</v>
+      </c>
+      <c r="K2" s="13">
+        <v>30</v>
+      </c>
+      <c r="L2" s="13">
+        <v>41</v>
+      </c>
+      <c r="M2" s="13">
+        <v>50</v>
+      </c>
+      <c r="N2" t="s">
+        <v>116</v>
+      </c>
+      <c r="P2" s="13">
+        <f>J2</f>
+        <v>29</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>L2/M2*20</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R2" s="13">
+        <f>P2+Q2</f>
+        <v>45.4</v>
+      </c>
+      <c r="S2" s="13">
+        <f>R2*2</f>
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3">
+        <v>93.2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3">
+        <v>570363</v>
+      </c>
+      <c r="I3" s="12">
+        <v>45901.652997685182</v>
+      </c>
+      <c r="J3" s="13">
+        <v>29</v>
+      </c>
+      <c r="K3" s="13">
+        <v>30</v>
+      </c>
+      <c r="L3" s="13">
+        <v>44</v>
+      </c>
+      <c r="M3" s="13">
+        <v>50</v>
+      </c>
+      <c r="N3" t="s">
+        <v>116</v>
+      </c>
+      <c r="P3" s="13">
+        <f t="shared" ref="P3:P42" si="0">J3</f>
+        <v>29</v>
+      </c>
+      <c r="Q3" s="13">
+        <f t="shared" ref="Q3:Q42" si="1">L3/M3*20</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R3" s="13">
+        <f t="shared" ref="R3:R42" si="2">P3+Q3</f>
+        <v>46.6</v>
+      </c>
+      <c r="S3" s="13">
+        <f t="shared" ref="S3:S42" si="3">R3*2</f>
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4">
+        <v>90.8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4">
+        <v>570365</v>
+      </c>
+      <c r="I4" s="12">
+        <v>45901.661666666667</v>
+      </c>
+      <c r="J4" s="13">
+        <v>29</v>
+      </c>
+      <c r="K4" s="13">
+        <v>30</v>
+      </c>
+      <c r="L4" s="13">
+        <v>41</v>
+      </c>
+      <c r="M4" s="13">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>116</v>
+      </c>
+      <c r="P4" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q4" s="13">
+        <f t="shared" si="1"/>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R4" s="13">
+        <f t="shared" si="2"/>
+        <v>45.4</v>
+      </c>
+      <c r="S4" s="13">
+        <f t="shared" si="3"/>
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5">
+        <v>85.2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5">
+        <v>570367</v>
+      </c>
+      <c r="I5" s="12">
+        <v>45901.622395833336</v>
+      </c>
+      <c r="J5" s="13">
+        <v>27</v>
+      </c>
+      <c r="K5" s="13">
+        <v>30</v>
+      </c>
+      <c r="L5" s="13">
+        <v>39</v>
+      </c>
+      <c r="M5" s="13">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>116</v>
+      </c>
+      <c r="P5" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q5" s="13">
+        <f t="shared" si="1"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="R5" s="13">
+        <f t="shared" si="2"/>
+        <v>42.6</v>
+      </c>
+      <c r="S5" s="13">
+        <f t="shared" si="3"/>
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>86</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>570371</v>
+      </c>
+      <c r="I6" s="12">
+        <v>45901.613310185188</v>
+      </c>
+      <c r="J6" s="13">
+        <v>27</v>
+      </c>
+      <c r="K6" s="13">
+        <v>30</v>
+      </c>
+      <c r="L6" s="13">
+        <v>40</v>
+      </c>
+      <c r="M6" s="13">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s">
+        <v>116</v>
+      </c>
+      <c r="P6" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q6" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R6" s="13">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="S6" s="13">
+        <f t="shared" si="3"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7">
+        <v>570372</v>
+      </c>
+      <c r="I7" s="12">
+        <v>45901.650208333333</v>
+      </c>
+      <c r="J7" s="13">
+        <v>29</v>
+      </c>
+      <c r="K7" s="13">
+        <v>30</v>
+      </c>
+      <c r="L7" s="13">
+        <v>40</v>
+      </c>
+      <c r="M7" s="13">
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="P7" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q7" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R7" s="13">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="S7" s="13">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>570373</v>
+      </c>
+      <c r="I8" s="12">
+        <v>45901.611851851849</v>
+      </c>
+      <c r="J8" s="13">
+        <v>23</v>
+      </c>
+      <c r="K8" s="13">
+        <v>30</v>
+      </c>
+      <c r="L8" s="13">
+        <v>38</v>
+      </c>
+      <c r="M8" s="13">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>116</v>
+      </c>
+      <c r="P8" s="13">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Q8" s="13">
+        <f t="shared" si="1"/>
+        <v>15.2</v>
+      </c>
+      <c r="R8" s="13">
+        <f t="shared" si="2"/>
+        <v>38.200000000000003</v>
+      </c>
+      <c r="S8" s="13">
+        <f t="shared" si="3"/>
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>91.2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9">
+        <v>570375</v>
+      </c>
+      <c r="I9" s="12">
+        <v>45901.625254629631</v>
+      </c>
+      <c r="J9" s="13">
+        <v>28</v>
+      </c>
+      <c r="K9" s="13">
+        <v>30</v>
+      </c>
+      <c r="L9" s="13">
+        <v>44</v>
+      </c>
+      <c r="M9" s="13">
+        <v>50</v>
+      </c>
+      <c r="N9" t="s">
+        <v>116</v>
+      </c>
+      <c r="P9" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q9" s="13">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R9" s="13">
+        <f t="shared" si="2"/>
+        <v>45.6</v>
+      </c>
+      <c r="S9" s="13">
+        <f t="shared" si="3"/>
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>89</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10">
+        <v>570376</v>
+      </c>
+      <c r="I10" s="12">
+        <v>45901.654178240744</v>
+      </c>
+      <c r="J10" s="13">
+        <v>28.5</v>
+      </c>
+      <c r="K10" s="13">
+        <v>30</v>
+      </c>
+      <c r="L10" s="13">
+        <v>40</v>
+      </c>
+      <c r="M10" s="13">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>117</v>
+      </c>
+      <c r="P10" s="13">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+      <c r="Q10" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R10" s="13">
+        <f t="shared" si="2"/>
+        <v>44.5</v>
+      </c>
+      <c r="S10" s="13">
+        <f t="shared" si="3"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11">
+        <v>84.8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11">
+        <v>570377</v>
+      </c>
+      <c r="I11" s="12">
+        <v>45901.656967592593</v>
+      </c>
+      <c r="J11" s="13">
+        <v>27</v>
+      </c>
+      <c r="K11" s="13">
+        <v>30</v>
+      </c>
+      <c r="L11" s="13">
+        <v>38.5</v>
+      </c>
+      <c r="M11" s="13">
+        <v>50</v>
+      </c>
+      <c r="N11" t="s">
+        <v>117</v>
+      </c>
+      <c r="P11" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q11" s="13">
+        <f t="shared" si="1"/>
+        <v>15.4</v>
+      </c>
+      <c r="R11" s="13">
+        <f t="shared" si="2"/>
+        <v>42.4</v>
+      </c>
+      <c r="S11" s="13">
+        <f t="shared" si="3"/>
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12">
+        <v>91.6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>570378</v>
+      </c>
+      <c r="I12" s="12">
+        <v>45901.659317129626</v>
+      </c>
+      <c r="J12" s="13">
+        <v>29</v>
+      </c>
+      <c r="K12" s="13">
+        <v>30</v>
+      </c>
+      <c r="L12" s="13">
+        <v>42</v>
+      </c>
+      <c r="M12" s="13">
+        <v>50</v>
+      </c>
+      <c r="N12" t="s">
+        <v>116</v>
+      </c>
+      <c r="P12" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q12" s="13">
+        <f t="shared" si="1"/>
+        <v>16.8</v>
+      </c>
+      <c r="R12" s="13">
+        <f t="shared" si="2"/>
+        <v>45.8</v>
+      </c>
+      <c r="S12" s="13">
+        <f t="shared" si="3"/>
+        <v>91.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13">
+        <v>570380</v>
+      </c>
+      <c r="I13" s="12">
+        <v>45901.618888888886</v>
+      </c>
+      <c r="J13" s="13">
+        <v>26</v>
+      </c>
+      <c r="K13" s="13">
+        <v>30</v>
+      </c>
+      <c r="L13" s="13">
+        <v>40</v>
+      </c>
+      <c r="M13" s="13">
+        <v>50</v>
+      </c>
+      <c r="N13" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13" s="13">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Q13" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R13" s="13">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="S13" s="13">
+        <f t="shared" si="3"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>570381</v>
+      </c>
+      <c r="I14" s="12">
+        <v>45901.615798611114</v>
+      </c>
+      <c r="J14" s="13">
+        <v>26</v>
+      </c>
+      <c r="K14" s="13">
+        <v>30</v>
+      </c>
+      <c r="L14" s="13">
+        <v>45</v>
+      </c>
+      <c r="M14" s="13">
+        <v>50</v>
+      </c>
+      <c r="N14" t="s">
+        <v>116</v>
+      </c>
+      <c r="P14" s="13">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="13">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="R14" s="13">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="S14" s="13">
+        <f t="shared" si="3"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15">
+        <v>83.6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15">
+        <v>570382</v>
+      </c>
+      <c r="I15" s="12">
+        <v>45901.618171296293</v>
+      </c>
+      <c r="J15" s="13">
+        <v>25</v>
+      </c>
+      <c r="K15" s="13">
+        <v>30</v>
+      </c>
+      <c r="L15" s="13">
+        <v>42</v>
+      </c>
+      <c r="M15" s="13">
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>116</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Q15" s="13">
+        <f t="shared" si="1"/>
+        <v>16.8</v>
+      </c>
+      <c r="R15" s="13">
+        <f t="shared" si="2"/>
+        <v>41.8</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="3"/>
+        <v>83.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16">
+        <v>90.199999999999989</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16">
+        <v>570390</v>
+      </c>
+      <c r="I16" s="12">
+        <v>45901.650578703702</v>
+      </c>
+      <c r="J16" s="13">
+        <v>28.5</v>
+      </c>
+      <c r="K16" s="13">
+        <v>30</v>
+      </c>
+      <c r="L16" s="13">
+        <v>41.5</v>
+      </c>
+      <c r="M16" s="13">
+        <v>50</v>
+      </c>
+      <c r="N16" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="13">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+      <c r="Q16" s="13">
+        <f t="shared" si="1"/>
+        <v>16.599999999999998</v>
+      </c>
+      <c r="R16" s="13">
+        <f t="shared" si="2"/>
+        <v>45.099999999999994</v>
+      </c>
+      <c r="S16" s="13">
+        <f t="shared" si="3"/>
+        <v>90.199999999999989</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17">
+        <v>570391</v>
+      </c>
+      <c r="I17" s="12">
+        <v>45901.658078703702</v>
+      </c>
+      <c r="J17" s="13">
+        <v>25.5</v>
+      </c>
+      <c r="K17" s="13">
+        <v>30</v>
+      </c>
+      <c r="L17" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="M17" s="13">
+        <v>50</v>
+      </c>
+      <c r="N17" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" s="13">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="Q17" s="13">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="R17" s="13">
+        <f t="shared" si="2"/>
+        <v>38.5</v>
+      </c>
+      <c r="S17" s="13">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18">
+        <v>83.2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18">
+        <v>570392</v>
+      </c>
+      <c r="I18" s="12">
+        <v>45901.656608796293</v>
+      </c>
+      <c r="J18" s="13">
+        <v>27</v>
+      </c>
+      <c r="K18" s="13">
+        <v>30</v>
+      </c>
+      <c r="L18" s="13">
+        <v>36.5</v>
+      </c>
+      <c r="M18" s="13">
+        <v>50</v>
+      </c>
+      <c r="N18" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q18" s="13">
+        <f t="shared" si="1"/>
+        <v>14.6</v>
+      </c>
+      <c r="R18" s="13">
+        <f t="shared" si="2"/>
+        <v>41.6</v>
+      </c>
+      <c r="S18" s="13">
+        <f t="shared" si="3"/>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>92</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19">
+        <v>570418</v>
+      </c>
+      <c r="I19" s="12">
+        <v>45901.652314814812</v>
+      </c>
+      <c r="J19" s="13">
+        <v>29</v>
+      </c>
+      <c r="K19" s="13">
+        <v>30</v>
+      </c>
+      <c r="L19" s="13">
+        <v>42.5</v>
+      </c>
+      <c r="M19" s="13">
+        <v>50</v>
+      </c>
+      <c r="N19" t="s">
+        <v>117</v>
+      </c>
+      <c r="P19" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q19" s="13">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="R19" s="13">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="S19" s="13">
+        <f t="shared" si="3"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20">
+        <v>88.4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20">
+        <v>570419</v>
+      </c>
+      <c r="I20" s="12">
+        <v>45901.646909722222</v>
+      </c>
+      <c r="J20" s="13">
+        <v>27</v>
+      </c>
+      <c r="K20" s="13">
+        <v>30</v>
+      </c>
+      <c r="L20" s="13">
+        <v>43</v>
+      </c>
+      <c r="M20" s="13">
+        <v>50</v>
+      </c>
+      <c r="N20" t="s">
+        <v>116</v>
+      </c>
+      <c r="P20" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q20" s="13">
+        <f t="shared" si="1"/>
+        <v>17.2</v>
+      </c>
+      <c r="R20" s="13">
+        <f t="shared" si="2"/>
+        <v>44.2</v>
+      </c>
+      <c r="S20" s="13">
+        <f t="shared" si="3"/>
+        <v>88.4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>87.2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21">
+        <v>570420</v>
+      </c>
+      <c r="I21" s="12">
+        <v>45901.648263888892</v>
+      </c>
+      <c r="J21" s="13">
+        <v>26</v>
+      </c>
+      <c r="K21" s="13">
+        <v>30</v>
+      </c>
+      <c r="L21" s="13">
+        <v>44</v>
+      </c>
+      <c r="M21" s="13">
+        <v>50</v>
+      </c>
+      <c r="N21" t="s">
+        <v>116</v>
+      </c>
+      <c r="P21" s="13">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="Q21" s="13">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R21" s="13">
+        <f t="shared" si="2"/>
+        <v>43.6</v>
+      </c>
+      <c r="S21" s="13">
+        <f t="shared" si="3"/>
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22">
+        <v>85.6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22">
+        <v>570421</v>
+      </c>
+      <c r="I22" s="12">
+        <v>45901.658599537041</v>
+      </c>
+      <c r="J22" s="13">
+        <v>28</v>
+      </c>
+      <c r="K22" s="13">
+        <v>30</v>
+      </c>
+      <c r="L22" s="13">
+        <v>37</v>
+      </c>
+      <c r="M22" s="13">
+        <v>50</v>
+      </c>
+      <c r="N22" t="s">
+        <v>116</v>
+      </c>
+      <c r="P22" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q22" s="13">
+        <f t="shared" si="1"/>
+        <v>14.8</v>
+      </c>
+      <c r="R22" s="13">
+        <f t="shared" si="2"/>
+        <v>42.8</v>
+      </c>
+      <c r="S22" s="13">
+        <f t="shared" si="3"/>
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23">
+        <v>89.2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23">
+        <v>570423</v>
+      </c>
+      <c r="I23" s="12">
+        <v>45901.626087962963</v>
+      </c>
+      <c r="J23" s="13">
+        <v>29</v>
+      </c>
+      <c r="K23" s="13">
+        <v>30</v>
+      </c>
+      <c r="L23" s="13">
+        <v>39</v>
+      </c>
+      <c r="M23" s="13">
+        <v>50</v>
+      </c>
+      <c r="N23" t="s">
+        <v>116</v>
+      </c>
+      <c r="P23" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q23" s="13">
+        <f t="shared" si="1"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="R23" s="13">
+        <f t="shared" si="2"/>
+        <v>44.6</v>
+      </c>
+      <c r="S23" s="13">
+        <f t="shared" si="3"/>
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24">
+        <v>99.2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24">
+        <v>570424</v>
+      </c>
+      <c r="I24" s="12">
+        <v>45901.646689814814</v>
+      </c>
+      <c r="J24" s="13">
+        <v>30</v>
+      </c>
+      <c r="K24" s="13">
+        <v>30</v>
+      </c>
+      <c r="L24" s="13">
+        <v>49</v>
+      </c>
+      <c r="M24" s="13">
+        <v>50</v>
+      </c>
+      <c r="N24" t="s">
+        <v>117</v>
+      </c>
+      <c r="P24" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="Q24" s="13">
+        <f t="shared" si="1"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R24" s="13">
+        <f t="shared" si="2"/>
+        <v>49.6</v>
+      </c>
+      <c r="S24" s="13">
+        <f t="shared" si="3"/>
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25">
+        <v>90</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25">
+        <v>570425</v>
+      </c>
+      <c r="I25" s="12">
+        <v>45901.650185185186</v>
+      </c>
+      <c r="J25" s="13">
+        <v>29</v>
+      </c>
+      <c r="K25" s="13">
+        <v>30</v>
+      </c>
+      <c r="L25" s="13">
+        <v>40</v>
+      </c>
+      <c r="M25" s="13">
+        <v>50</v>
+      </c>
+      <c r="N25" t="s">
+        <v>117</v>
+      </c>
+      <c r="P25" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q25" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R25" s="13">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="S25" s="13">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26">
+        <v>83.6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26">
+        <v>570427</v>
+      </c>
+      <c r="I26" s="12">
+        <v>45901.659108796295</v>
+      </c>
+      <c r="J26" s="13">
+        <v>29</v>
+      </c>
+      <c r="K26" s="13">
+        <v>30</v>
+      </c>
+      <c r="L26" s="13">
+        <v>32</v>
+      </c>
+      <c r="M26" s="13">
+        <v>50</v>
+      </c>
+      <c r="N26" t="s">
+        <v>116</v>
+      </c>
+      <c r="P26" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q26" s="13">
+        <f t="shared" si="1"/>
+        <v>12.8</v>
+      </c>
+      <c r="R26" s="13">
+        <f t="shared" si="2"/>
+        <v>41.8</v>
+      </c>
+      <c r="S26" s="13">
+        <f t="shared" si="3"/>
+        <v>83.6</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27">
+        <v>85.6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27">
+        <v>570434</v>
+      </c>
+      <c r="I27" s="12">
+        <v>45901.631342592591</v>
+      </c>
+      <c r="J27" s="13">
+        <v>28</v>
+      </c>
+      <c r="K27" s="13">
+        <v>30</v>
+      </c>
+      <c r="L27" s="13">
+        <v>37</v>
+      </c>
+      <c r="M27" s="13">
+        <v>50</v>
+      </c>
+      <c r="N27" t="s">
+        <v>116</v>
+      </c>
+      <c r="P27" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q27" s="13">
+        <f t="shared" si="1"/>
+        <v>14.8</v>
+      </c>
+      <c r="R27" s="13">
+        <f t="shared" si="2"/>
+        <v>42.8</v>
+      </c>
+      <c r="S27" s="13">
+        <f t="shared" si="3"/>
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28">
+        <v>88</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28">
+        <v>570442</v>
+      </c>
+      <c r="I28" s="12">
+        <v>45901.660555555558</v>
+      </c>
+      <c r="J28" s="13">
+        <v>28</v>
+      </c>
+      <c r="K28" s="13">
+        <v>30</v>
+      </c>
+      <c r="L28" s="13">
+        <v>40</v>
+      </c>
+      <c r="M28" s="13">
+        <v>50</v>
+      </c>
+      <c r="N28" t="s">
+        <v>116</v>
+      </c>
+      <c r="P28" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q28" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R28" s="13">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="S28" s="13">
+        <f t="shared" si="3"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>91.2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29">
+        <v>570444</v>
+      </c>
+      <c r="I29" s="12">
+        <v>45901.617974537039</v>
+      </c>
+      <c r="J29" s="13">
+        <v>28</v>
+      </c>
+      <c r="K29" s="13">
+        <v>30</v>
+      </c>
+      <c r="L29" s="13">
+        <v>44</v>
+      </c>
+      <c r="M29" s="13">
+        <v>50</v>
+      </c>
+      <c r="N29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P29" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q29" s="13">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R29" s="13">
+        <f t="shared" si="2"/>
+        <v>45.6</v>
+      </c>
+      <c r="S29" s="13">
+        <f t="shared" si="3"/>
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30">
+        <v>87.6</v>
+      </c>
+      <c r="G30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30">
+        <v>570468</v>
+      </c>
+      <c r="I30" s="12">
+        <v>45901.618796296294</v>
+      </c>
+      <c r="J30" s="13">
+        <v>27</v>
+      </c>
+      <c r="K30" s="13">
+        <v>30</v>
+      </c>
+      <c r="L30" s="13">
+        <v>42</v>
+      </c>
+      <c r="M30" s="13">
+        <v>50</v>
+      </c>
+      <c r="N30" t="s">
+        <v>120</v>
+      </c>
+      <c r="P30" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q30" s="13">
+        <f t="shared" si="1"/>
+        <v>16.8</v>
+      </c>
+      <c r="R30" s="13">
+        <f t="shared" si="2"/>
+        <v>43.8</v>
+      </c>
+      <c r="S30" s="13">
+        <f t="shared" si="3"/>
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31">
+        <v>570469</v>
+      </c>
+      <c r="I31" s="12">
+        <v>45901.652314814812</v>
+      </c>
+      <c r="J31" s="13">
+        <v>28</v>
+      </c>
+      <c r="K31" s="13">
+        <v>30</v>
+      </c>
+      <c r="L31" s="13">
+        <v>40</v>
+      </c>
+      <c r="M31" s="13">
+        <v>50</v>
+      </c>
+      <c r="N31" t="s">
+        <v>116</v>
+      </c>
+      <c r="P31" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q31" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R31" s="13">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="S31" s="13">
+        <f t="shared" si="3"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32">
+        <v>85.6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32">
+        <v>570532</v>
+      </c>
+      <c r="I32" s="12">
+        <v>45901.657048611109</v>
+      </c>
+      <c r="J32" s="13">
+        <v>28</v>
+      </c>
+      <c r="K32" s="13">
+        <v>30</v>
+      </c>
+      <c r="L32" s="13">
+        <v>37</v>
+      </c>
+      <c r="M32" s="13">
+        <v>50</v>
+      </c>
+      <c r="N32" t="s">
+        <v>116</v>
+      </c>
+      <c r="P32" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q32" s="13">
+        <f t="shared" si="1"/>
+        <v>14.8</v>
+      </c>
+      <c r="R32" s="13">
+        <f t="shared" si="2"/>
+        <v>42.8</v>
+      </c>
+      <c r="S32" s="13">
+        <f t="shared" si="3"/>
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33">
+        <v>570534</v>
+      </c>
+      <c r="I33" s="12">
+        <v>45901.623761574076</v>
+      </c>
+      <c r="J33" s="13">
+        <v>28</v>
+      </c>
+      <c r="K33" s="13">
+        <v>30</v>
+      </c>
+      <c r="L33" s="13">
+        <v>40</v>
+      </c>
+      <c r="M33" s="13">
+        <v>50</v>
+      </c>
+      <c r="N33" t="s">
+        <v>120</v>
+      </c>
+      <c r="P33" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q33" s="13">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="R33" s="13">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="S33" s="13">
+        <f t="shared" si="3"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34">
+        <v>93.6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34">
+        <v>570535</v>
+      </c>
+      <c r="I34" s="12">
+        <v>45901.653784722221</v>
+      </c>
+      <c r="J34" s="13">
+        <v>28</v>
+      </c>
+      <c r="K34" s="13">
+        <v>30</v>
+      </c>
+      <c r="L34" s="13">
+        <v>47</v>
+      </c>
+      <c r="M34" s="13">
+        <v>50</v>
+      </c>
+      <c r="N34" t="s">
+        <v>116</v>
+      </c>
+      <c r="P34" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q34" s="13">
+        <f t="shared" si="1"/>
+        <v>18.799999999999997</v>
+      </c>
+      <c r="R34" s="13">
+        <f t="shared" si="2"/>
+        <v>46.8</v>
+      </c>
+      <c r="S34" s="13">
+        <f t="shared" si="3"/>
+        <v>93.6</v>
+      </c>
+    </row>
+    <row r="35" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35">
+        <v>87.6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35">
+        <v>570536</v>
+      </c>
+      <c r="I35" s="12">
+        <v>45901.654479166667</v>
+      </c>
+      <c r="J35" s="13">
+        <v>29</v>
+      </c>
+      <c r="K35" s="13">
+        <v>30</v>
+      </c>
+      <c r="L35" s="13">
+        <v>37</v>
+      </c>
+      <c r="M35" s="13">
+        <v>50</v>
+      </c>
+      <c r="N35" t="s">
+        <v>116</v>
+      </c>
+      <c r="P35" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q35" s="13">
+        <f t="shared" si="1"/>
+        <v>14.8</v>
+      </c>
+      <c r="R35" s="13">
+        <f t="shared" si="2"/>
+        <v>43.8</v>
+      </c>
+      <c r="S35" s="13">
+        <f t="shared" si="3"/>
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36">
+        <v>89.2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36">
+        <v>570537</v>
+      </c>
+      <c r="I36" s="12">
+        <v>45901.619791666664</v>
+      </c>
+      <c r="J36" s="13">
+        <v>27</v>
+      </c>
+      <c r="K36" s="13">
+        <v>30</v>
+      </c>
+      <c r="L36" s="13">
+        <v>44</v>
+      </c>
+      <c r="M36" s="13">
+        <v>50</v>
+      </c>
+      <c r="N36" t="s">
+        <v>116</v>
+      </c>
+      <c r="P36" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q36" s="13">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="R36" s="13">
+        <f t="shared" si="2"/>
+        <v>44.6</v>
+      </c>
+      <c r="S36" s="13">
+        <f t="shared" si="3"/>
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37">
+        <v>94</v>
+      </c>
+      <c r="G37" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37">
+        <v>570538</v>
+      </c>
+      <c r="I37" s="12">
+        <v>45901.617754629631</v>
+      </c>
+      <c r="J37" s="13">
+        <v>27</v>
+      </c>
+      <c r="K37" s="13">
+        <v>30</v>
+      </c>
+      <c r="L37" s="13">
+        <v>50</v>
+      </c>
+      <c r="M37" s="13">
+        <v>50</v>
+      </c>
+      <c r="N37" t="s">
+        <v>116</v>
+      </c>
+      <c r="P37" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q37" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="R37" s="13">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="S37" s="13">
+        <f t="shared" si="3"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38">
+        <v>94</v>
+      </c>
+      <c r="G38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <v>570539</v>
+      </c>
+      <c r="I38" s="12">
+        <v>45901.654849537037</v>
+      </c>
+      <c r="J38" s="13">
+        <v>29</v>
+      </c>
+      <c r="K38" s="13">
+        <v>30</v>
+      </c>
+      <c r="L38" s="13">
+        <v>45</v>
+      </c>
+      <c r="M38" s="13">
+        <v>50</v>
+      </c>
+      <c r="N38" t="s">
+        <v>116</v>
+      </c>
+      <c r="P38" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q38" s="13">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="R38" s="13">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="S38" s="13">
+        <f t="shared" si="3"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39">
+        <v>82.4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39">
+        <v>570615</v>
+      </c>
+      <c r="I39" s="12">
+        <v>45901.624722222223</v>
+      </c>
+      <c r="J39" s="13">
+        <v>28</v>
+      </c>
+      <c r="K39" s="13">
+        <v>30</v>
+      </c>
+      <c r="L39" s="13">
+        <v>33</v>
+      </c>
+      <c r="M39" s="13">
+        <v>50</v>
+      </c>
+      <c r="N39" t="s">
+        <v>116</v>
+      </c>
+      <c r="P39" s="13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="Q39" s="13">
+        <f t="shared" si="1"/>
+        <v>13.200000000000001</v>
+      </c>
+      <c r="R39" s="13">
+        <f t="shared" si="2"/>
+        <v>41.2</v>
+      </c>
+      <c r="S39" s="13">
+        <f t="shared" si="3"/>
+        <v>82.4</v>
+      </c>
+    </row>
+    <row r="40" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40">
+        <v>85.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40">
+        <v>570768</v>
+      </c>
+      <c r="I40" s="12">
+        <v>45901.653912037036</v>
+      </c>
+      <c r="J40" s="13">
+        <v>27</v>
+      </c>
+      <c r="K40" s="13">
+        <v>30</v>
+      </c>
+      <c r="L40" s="13">
+        <v>39</v>
+      </c>
+      <c r="M40" s="13">
+        <v>50</v>
+      </c>
+      <c r="N40" t="s">
+        <v>116</v>
+      </c>
+      <c r="P40" s="13">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Q40" s="13">
+        <f t="shared" si="1"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="R40" s="13">
+        <f t="shared" si="2"/>
+        <v>42.6</v>
+      </c>
+      <c r="S40" s="13">
+        <f t="shared" si="3"/>
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41">
+        <v>90.4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41">
+        <v>570816</v>
+      </c>
+      <c r="I41" s="12">
+        <v>45901.654398148145</v>
+      </c>
+      <c r="J41" s="13">
+        <v>30</v>
+      </c>
+      <c r="K41" s="13">
+        <v>30</v>
+      </c>
+      <c r="L41" s="13">
+        <v>38</v>
+      </c>
+      <c r="M41" s="13">
+        <v>50</v>
+      </c>
+      <c r="N41" t="s">
+        <v>116</v>
+      </c>
+      <c r="P41" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="Q41" s="13">
+        <f t="shared" si="1"/>
+        <v>15.2</v>
+      </c>
+      <c r="R41" s="13">
+        <f t="shared" si="2"/>
+        <v>45.2</v>
+      </c>
+      <c r="S41" s="13">
+        <f t="shared" si="3"/>
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="42" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42">
+        <v>82.8</v>
+      </c>
+      <c r="G42" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42">
+        <v>570838</v>
+      </c>
+      <c r="I42" s="12">
+        <v>45901.632245370369</v>
+      </c>
+      <c r="J42" s="13">
+        <v>29</v>
+      </c>
+      <c r="K42" s="13">
+        <v>30</v>
+      </c>
+      <c r="L42" s="13">
+        <v>31</v>
+      </c>
+      <c r="M42" s="13">
+        <v>50</v>
+      </c>
+      <c r="N42" t="s">
+        <v>116</v>
+      </c>
+      <c r="P42" s="13">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="Q42" s="13">
+        <f t="shared" si="1"/>
+        <v>12.4</v>
+      </c>
+      <c r="R42" s="13">
+        <f t="shared" si="2"/>
+        <v>41.4</v>
+      </c>
+      <c r="S42" s="13">
+        <f t="shared" si="3"/>
+        <v>82.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:D42">
+    <sortCondition ref="C2:C42"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C4B216-67FA-4FCF-8DDE-01EDC96B59F8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5022EBD8-D20C-4E72-9268-F29CD9CE10B9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="PLSQL" sheetId="2" r:id="rId3"/>
     <sheet name="Java" sheetId="4" r:id="rId4"/>
     <sheet name="Spring" sheetId="5" r:id="rId5"/>
+    <sheet name="HTML_CSS_Js" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="131">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -418,6 +419,15 @@
   </si>
   <si>
     <t>570426</t>
+  </si>
+  <si>
+    <t>Employee Id</t>
+  </si>
+  <si>
+    <t>%age</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JS</t>
   </si>
 </sst>
 </file>
@@ -836,18 +846,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CBB81-7004-434A-99AB-007D8B0836DA}">
-  <dimension ref="B2:H43"/>
+  <dimension ref="B2:I43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.88671875" customWidth="1"/>
-    <col min="8" max="8" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="6.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,9 +876,12 @@
       <c r="G2" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="G3" s="4">
         <v>0.91599999999999993</v>
       </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H3" s="4">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
@@ -908,9 +924,12 @@
       <c r="G4" s="4">
         <v>0.83599999999999997</v>
       </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H4" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
@@ -929,9 +948,12 @@
       <c r="G5" s="4">
         <v>0.90799999999999992</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H5" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
@@ -950,9 +972,12 @@
       <c r="G6" s="4">
         <v>0.93200000000000005</v>
       </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -971,9 +996,12 @@
       <c r="G7" s="4">
         <v>0.90799999999999992</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -992,9 +1020,12 @@
       <c r="G8" s="4">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1013,9 +1044,12 @@
       <c r="G9" s="4">
         <v>0.86</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1034,9 +1068,12 @@
       <c r="G10" s="4">
         <v>0.9</v>
       </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1055,9 +1092,12 @@
       <c r="G11" s="4">
         <v>0.76400000000000001</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1076,9 +1116,12 @@
       <c r="G12" s="4">
         <v>0.91200000000000003</v>
       </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1097,9 +1140,12 @@
       <c r="G13" s="4">
         <v>0.89</v>
       </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1118,9 +1164,12 @@
       <c r="G14" s="4">
         <v>0.84799999999999998</v>
       </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1139,9 +1188,12 @@
       <c r="G15" s="4">
         <v>0.84</v>
       </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="4">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1160,9 +1212,12 @@
       <c r="G16" s="4">
         <v>0.88</v>
       </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -1181,9 +1236,12 @@
       <c r="G17" s="4">
         <v>0.83599999999999997</v>
       </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1202,9 +1260,12 @@
       <c r="G18" s="4">
         <v>0.90199999999999991</v>
       </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1223,9 +1284,12 @@
       <c r="G19" s="4">
         <v>0.77</v>
       </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1244,9 +1308,12 @@
       <c r="G20" s="4">
         <v>0.83200000000000007</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1265,9 +1332,12 @@
       <c r="G21" s="4">
         <v>0.92</v>
       </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="4">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1286,9 +1356,12 @@
       <c r="G22" s="4">
         <v>0.88400000000000001</v>
       </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H22" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1307,9 +1380,12 @@
       <c r="G23" s="4">
         <v>0.872</v>
       </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H23" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1328,9 +1404,12 @@
       <c r="G24" s="4">
         <v>0.85599999999999998</v>
       </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="4">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1349,9 +1428,12 @@
       <c r="G25" s="4">
         <v>0.89200000000000002</v>
       </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H25" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
@@ -1370,9 +1452,12 @@
       <c r="G26" s="4">
         <v>0.99199999999999999</v>
       </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H26" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1391,9 +1476,12 @@
       <c r="G27" s="4">
         <v>0.9</v>
       </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H27" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
@@ -1412,9 +1500,12 @@
       <c r="G28" s="4">
         <v>0.85599999999999998</v>
       </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H28" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1433,9 +1524,12 @@
       <c r="G29" s="4">
         <v>0.88</v>
       </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H29" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
@@ -1454,9 +1548,12 @@
       <c r="G30" s="4">
         <v>0.91200000000000003</v>
       </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H30" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
@@ -1475,9 +1572,12 @@
       <c r="G31" s="4">
         <v>0.87599999999999989</v>
       </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H31" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>23</v>
       </c>
@@ -1496,9 +1596,12 @@
       <c r="G32" s="4">
         <v>0.88</v>
       </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H32" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
@@ -1517,9 +1620,12 @@
       <c r="G33" s="4">
         <v>0.85599999999999998</v>
       </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H33" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
@@ -1538,9 +1644,12 @@
       <c r="G34" s="4">
         <v>0.88</v>
       </c>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H34" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
@@ -1559,9 +1668,12 @@
       <c r="G35" s="4">
         <v>0.93599999999999994</v>
       </c>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H35" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
@@ -1580,9 +1692,12 @@
       <c r="G36" s="4">
         <v>0.87599999999999989</v>
       </c>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H36" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>17</v>
       </c>
@@ -1601,9 +1716,12 @@
       <c r="G37" s="4">
         <v>0.89200000000000002</v>
       </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H37" s="4">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1622,9 +1740,12 @@
       <c r="G38" s="4">
         <v>0.94</v>
       </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H38" s="4">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>20</v>
       </c>
@@ -1643,9 +1764,12 @@
       <c r="G39" s="4">
         <v>0.94</v>
       </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H39" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
@@ -1664,9 +1788,12 @@
       <c r="G40" s="4">
         <v>0.82400000000000007</v>
       </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H40" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
@@ -1685,9 +1812,12 @@
       <c r="G41" s="4">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H41" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>86</v>
       </c>
@@ -1706,9 +1836,12 @@
       <c r="G42" s="4">
         <v>0.90400000000000003</v>
       </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H42" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>87</v>
       </c>
@@ -1727,7 +1860,10 @@
       <c r="G43" s="4">
         <v>0.82799999999999996</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H43" s="4">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="I43" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6729,4 +6865,903 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9423959F-C99B-473C-906E-3B1CDC712C50}">
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2">
+        <v>570427</v>
+      </c>
+      <c r="C2" s="12">
+        <v>45904.516076388885</v>
+      </c>
+      <c r="D2">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <f>D2/E2</f>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3">
+        <v>570376</v>
+      </c>
+      <c r="C3" s="12">
+        <v>45904.515509259261</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F42" si="0">D3/E3</f>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4">
+        <v>570378</v>
+      </c>
+      <c r="C4" s="12">
+        <v>45904.5153587963</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0.96666666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5">
+        <v>570377</v>
+      </c>
+      <c r="C5" s="12">
+        <v>45904.514918981484</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6">
+        <v>570372</v>
+      </c>
+      <c r="C6" s="12">
+        <v>45904.51462962963</v>
+      </c>
+      <c r="D6">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7">
+        <v>570536</v>
+      </c>
+      <c r="C7" s="12">
+        <v>45904.51457175926</v>
+      </c>
+      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8">
+        <v>570539</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45904.514548611114</v>
+      </c>
+      <c r="D8">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9">
+        <v>570367</v>
+      </c>
+      <c r="C9" s="12">
+        <v>45904.514224537037</v>
+      </c>
+      <c r="D9">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10">
+        <v>570816</v>
+      </c>
+      <c r="C10" s="12">
+        <v>45904.514166666668</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11">
+        <v>570434</v>
+      </c>
+      <c r="C11" s="12">
+        <v>45904.513807870368</v>
+      </c>
+      <c r="D11">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12">
+        <v>570468</v>
+      </c>
+      <c r="C12" s="12">
+        <v>45904.513402777775</v>
+      </c>
+      <c r="D12">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13">
+        <v>570391</v>
+      </c>
+      <c r="C13" s="12">
+        <v>45904.513333333336</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>570425</v>
+      </c>
+      <c r="C14" s="12">
+        <v>45904.513090277775</v>
+      </c>
+      <c r="D14">
+        <v>28</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15">
+        <v>570838</v>
+      </c>
+      <c r="C15" s="12">
+        <v>45904.512777777774</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16">
+        <v>570420</v>
+      </c>
+      <c r="C16" s="12">
+        <v>45904.512731481482</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17">
+        <v>570534</v>
+      </c>
+      <c r="C17" s="12">
+        <v>45904.512650462966</v>
+      </c>
+      <c r="D17">
+        <v>26</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>570444</v>
+      </c>
+      <c r="C18" s="12">
+        <v>45904.512523148151</v>
+      </c>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19">
+        <v>570442</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45904.512488425928</v>
+      </c>
+      <c r="D19">
+        <v>28</v>
+      </c>
+      <c r="E19">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20">
+        <v>570375</v>
+      </c>
+      <c r="C20" s="12">
+        <v>45904.512407407405</v>
+      </c>
+      <c r="D20">
+        <v>28</v>
+      </c>
+      <c r="E20">
+        <v>30</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21">
+        <v>570615</v>
+      </c>
+      <c r="C21" s="12">
+        <v>45904.51226851852</v>
+      </c>
+      <c r="D21">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>30</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22">
+        <v>570421</v>
+      </c>
+      <c r="C22" s="12">
+        <v>45904.512245370373</v>
+      </c>
+      <c r="D22">
+        <v>23</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>0.76666666666666672</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23">
+        <v>570532</v>
+      </c>
+      <c r="C23" s="12">
+        <v>45904.51221064815</v>
+      </c>
+      <c r="D23">
+        <v>26</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24">
+        <v>570469</v>
+      </c>
+      <c r="C24" s="12">
+        <v>45904.512199074074</v>
+      </c>
+      <c r="D24">
+        <v>26</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25">
+        <v>570418</v>
+      </c>
+      <c r="C25" s="12">
+        <v>45904.512013888889</v>
+      </c>
+      <c r="D25">
+        <v>29</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>0.96666666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26">
+        <v>570365</v>
+      </c>
+      <c r="C26" s="12">
+        <v>45904.511956018519</v>
+      </c>
+      <c r="D26">
+        <v>27</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27">
+        <v>570390</v>
+      </c>
+      <c r="C27" s="12">
+        <v>45904.511805555558</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28">
+        <v>570768</v>
+      </c>
+      <c r="C28" s="12">
+        <v>45904.511354166665</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29">
+        <v>570362</v>
+      </c>
+      <c r="C29" s="12">
+        <v>45904.511319444442</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30">
+        <v>570392</v>
+      </c>
+      <c r="C30" s="12">
+        <v>45904.511261574073</v>
+      </c>
+      <c r="D30">
+        <v>26</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31">
+        <v>570363</v>
+      </c>
+      <c r="C31" s="12">
+        <v>45904.511145833334</v>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+      <c r="E31">
+        <v>30</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32">
+        <v>570423</v>
+      </c>
+      <c r="C32" s="12">
+        <v>45904.510613425926</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33">
+        <v>570371</v>
+      </c>
+      <c r="C33" s="12">
+        <v>45904.509502314817</v>
+      </c>
+      <c r="D33">
+        <v>26</v>
+      </c>
+      <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>570419</v>
+      </c>
+      <c r="C34" s="12">
+        <v>45904.509363425925</v>
+      </c>
+      <c r="D34">
+        <v>27</v>
+      </c>
+      <c r="E34">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35">
+        <v>570538</v>
+      </c>
+      <c r="C35" s="12">
+        <v>45904.509155092594</v>
+      </c>
+      <c r="D35">
+        <v>29</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>0.96666666666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36">
+        <v>570381</v>
+      </c>
+      <c r="C36" s="12">
+        <v>45904.509108796294</v>
+      </c>
+      <c r="D36">
+        <v>28</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37">
+        <v>570535</v>
+      </c>
+      <c r="C37" s="12">
+        <v>45904.509050925924</v>
+      </c>
+      <c r="D37">
+        <v>27</v>
+      </c>
+      <c r="E37">
+        <v>30</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38">
+        <v>570380</v>
+      </c>
+      <c r="C38" s="12">
+        <v>45904.508877314816</v>
+      </c>
+      <c r="D38">
+        <v>23</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>0.76666666666666672</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39">
+        <v>570373</v>
+      </c>
+      <c r="C39" s="12">
+        <v>45904.508726851855</v>
+      </c>
+      <c r="D39">
+        <v>24</v>
+      </c>
+      <c r="E39">
+        <v>30</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40">
+        <v>570424</v>
+      </c>
+      <c r="C40" s="12">
+        <v>45904.508298611108</v>
+      </c>
+      <c r="D40">
+        <v>27</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41">
+        <v>570537</v>
+      </c>
+      <c r="C41" s="12">
+        <v>45904.506481481483</v>
+      </c>
+      <c r="D41">
+        <v>22</v>
+      </c>
+      <c r="E41">
+        <v>30</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>0.73333333333333328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42">
+        <v>570382</v>
+      </c>
+      <c r="C42" s="12">
+        <v>45904.505289351851</v>
+      </c>
+      <c r="D42">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>30</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5022EBD8-D20C-4E72-9268-F29CD9CE10B9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A49BB2B-8B42-44D8-881C-CDFBCCFF804F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Java" sheetId="4" r:id="rId4"/>
     <sheet name="Spring" sheetId="5" r:id="rId5"/>
     <sheet name="HTML_CSS_Js" sheetId="6" r:id="rId6"/>
+    <sheet name="ReactJs" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="137">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -428,6 +429,24 @@
   </si>
   <si>
     <t>HTML, CSS, JS</t>
+  </si>
+  <si>
+    <t>Mcq (30)</t>
+  </si>
+  <si>
+    <t>Coding (20)</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>00570427</t>
+  </si>
+  <si>
+    <t>ReactJs</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -514,7 +533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -531,6 +550,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,18 +867,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CBB81-7004-434A-99AB-007D8B0836DA}">
-  <dimension ref="B2:I43"/>
+  <dimension ref="B2:J43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="6.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.88671875" customWidth="1"/>
+    <col min="10" max="10" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,9 +900,12 @@
       <c r="H2" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
@@ -903,9 +927,12 @@
       <c r="H3" s="4">
         <v>0.96666666666666667</v>
       </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="4">
+        <v>0.80666666666666653</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
@@ -927,9 +954,12 @@
       <c r="H4" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
@@ -951,9 +981,12 @@
       <c r="H5" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="4">
+        <v>0.87333333333333329</v>
+      </c>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
@@ -975,9 +1008,12 @@
       <c r="H6" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="15">
+        <v>0.67333333333333334</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -999,9 +1035,12 @@
       <c r="H7" s="4">
         <v>0.9</v>
       </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1023,9 +1062,12 @@
       <c r="H8" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I8" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1047,9 +1089,12 @@
       <c r="H9" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1071,9 +1116,12 @@
       <c r="H10" s="4">
         <v>0.9</v>
       </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I10" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1095,9 +1143,12 @@
       <c r="H11" s="4">
         <v>0.8</v>
       </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I11" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1119,9 +1170,12 @@
       <c r="H12" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="4">
+        <v>0.81333333333333324</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1143,9 +1197,12 @@
       <c r="H13" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I13" s="4">
+        <v>0.94666666666666655</v>
+      </c>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1167,9 +1224,12 @@
       <c r="H14" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1191,9 +1251,12 @@
       <c r="H15" s="4">
         <v>0.76666666666666672</v>
       </c>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1215,9 +1278,12 @@
       <c r="H16" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I16" s="4">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -1239,9 +1305,12 @@
       <c r="H17" s="4">
         <v>0.8</v>
       </c>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="4">
+        <v>0.87333333333333341</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1263,9 +1332,12 @@
       <c r="H18" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1287,9 +1359,12 @@
       <c r="H19" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I19" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
@@ -1311,9 +1386,12 @@
       <c r="H20" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="4">
+        <v>0.88666666666666671</v>
+      </c>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1335,9 +1413,12 @@
       <c r="H21" s="4">
         <v>0.96666666666666667</v>
       </c>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="4">
+        <v>0.90666666666666673</v>
+      </c>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1359,9 +1440,12 @@
       <c r="H22" s="4">
         <v>0.9</v>
       </c>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I22" s="4">
+        <v>0.88666666666666671</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
@@ -1383,9 +1467,12 @@
       <c r="H23" s="4">
         <v>0.8</v>
       </c>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I23" s="4">
+        <v>0.74666666666666659</v>
+      </c>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1407,9 +1494,12 @@
       <c r="H24" s="4">
         <v>0.76666666666666672</v>
       </c>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I24" s="4">
+        <v>0.78666666666666663</v>
+      </c>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
@@ -1431,9 +1521,12 @@
       <c r="H25" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I25" s="4">
+        <v>0.72666666666666668</v>
+      </c>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>8</v>
       </c>
@@ -1455,9 +1548,12 @@
       <c r="H26" s="4">
         <v>0.9</v>
       </c>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I26" s="4">
+        <v>0.89333333333333342</v>
+      </c>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1479,9 +1575,12 @@
       <c r="H27" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I27" s="4">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
@@ -1503,9 +1602,12 @@
       <c r="H28" s="4">
         <v>0.8</v>
       </c>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I28" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1527,9 +1629,12 @@
       <c r="H29" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I29" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
@@ -1551,9 +1656,12 @@
       <c r="H30" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I30" s="4">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
@@ -1575,9 +1683,12 @@
       <c r="H31" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I31" s="4">
+        <v>0.91333333333333344</v>
+      </c>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>23</v>
       </c>
@@ -1599,9 +1710,12 @@
       <c r="H32" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I32" s="4">
+        <v>0.78666666666666674</v>
+      </c>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
@@ -1623,9 +1737,12 @@
       <c r="H33" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I33" s="3"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I33" s="4">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
@@ -1647,9 +1764,12 @@
       <c r="H34" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I34" s="4">
+        <v>0.93333333333333346</v>
+      </c>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
@@ -1671,9 +1791,12 @@
       <c r="H35" s="4">
         <v>0.9</v>
       </c>
-      <c r="I35" s="3"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I35" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
@@ -1695,9 +1818,12 @@
       <c r="H36" s="4">
         <v>0.9</v>
       </c>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I36" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
         <v>17</v>
       </c>
@@ -1719,9 +1845,12 @@
       <c r="H37" s="4">
         <v>0.73333333333333328</v>
       </c>
-      <c r="I37" s="3"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I37" s="4">
+        <v>0.84666666666666668</v>
+      </c>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1743,9 +1872,12 @@
       <c r="H38" s="4">
         <v>0.96666666666666667</v>
       </c>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I38" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
         <v>20</v>
       </c>
@@ -1767,9 +1899,12 @@
       <c r="H39" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I39" s="4">
+        <v>0.71333333333333326</v>
+      </c>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
@@ -1791,9 +1926,12 @@
       <c r="H40" s="4">
         <v>0.8</v>
       </c>
-      <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I40" s="4">
+        <v>0.90666666666666673</v>
+      </c>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
@@ -1815,9 +1953,12 @@
       <c r="H41" s="4">
         <v>0.9</v>
       </c>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I41" s="4">
+        <v>0.78666666666666663</v>
+      </c>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>86</v>
       </c>
@@ -1839,9 +1980,12 @@
       <c r="H42" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I42" s="4">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>87</v>
       </c>
@@ -1863,7 +2007,10 @@
       <c r="H43" s="4">
         <v>0.93333333333333335</v>
       </c>
-      <c r="I43" s="3"/>
+      <c r="I43" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="J43" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7764,4 +7911,1996 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{379B70B4-E4BA-416C-BDA9-CDEC7B2C6BC8}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>29</v>
+      </c>
+      <c r="D2">
+        <v>11.333333333333332</v>
+      </c>
+      <c r="E2">
+        <v>0.80666666666666653</v>
+      </c>
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2">
+        <v>29</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+      <c r="K2">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M16" si="0">I2</f>
+        <v>29</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N16" si="1">K2/L2*20</f>
+        <v>11.333333333333332</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ref="O2:O16" si="2">SUM(M2,N2)/50</f>
+        <v>0.80666666666666653</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>0.84</v>
+      </c>
+      <c r="G3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I3">
+        <v>28</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>21</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="2"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="E4">
+        <v>0.87333333333333329</v>
+      </c>
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>570362</v>
+      </c>
+      <c r="I4">
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="1"/>
+        <v>14.666666666666666</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="2"/>
+        <v>0.87333333333333329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="E5">
+        <v>0.67333333333333334</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5">
+        <v>570363</v>
+      </c>
+      <c r="I5">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="K5">
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="2"/>
+        <v>0.67333333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>0.94</v>
+      </c>
+      <c r="G6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>570365</v>
+      </c>
+      <c r="I6">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="2"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="E7">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7">
+        <v>570367</v>
+      </c>
+      <c r="I7">
+        <v>28</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>23</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E8">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8">
+        <v>570371</v>
+      </c>
+      <c r="I8">
+        <v>26</v>
+      </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>30</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="2"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9">
+        <v>570372</v>
+      </c>
+      <c r="I9">
+        <v>29</v>
+      </c>
+      <c r="J9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>30</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>570373</v>
+      </c>
+      <c r="I10">
+        <v>26</v>
+      </c>
+      <c r="J10">
+        <v>30</v>
+      </c>
+      <c r="K10">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>30</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="2"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="E11">
+        <v>0.81333333333333324</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11">
+        <v>570375</v>
+      </c>
+      <c r="I11">
+        <v>26</v>
+      </c>
+      <c r="J11">
+        <v>30</v>
+      </c>
+      <c r="K11">
+        <v>22</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>14.666666666666666</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="2"/>
+        <v>0.81333333333333324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="E12">
+        <v>0.94666666666666655</v>
+      </c>
+      <c r="G12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12">
+        <v>570376</v>
+      </c>
+      <c r="I12">
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <v>30</v>
+      </c>
+      <c r="K12">
+        <v>29</v>
+      </c>
+      <c r="L12">
+        <v>30</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="2"/>
+        <v>0.94666666666666655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13">
+        <v>28</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>0.8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13">
+        <v>570377</v>
+      </c>
+      <c r="I13">
+        <v>28</v>
+      </c>
+      <c r="J13">
+        <v>30</v>
+      </c>
+      <c r="K13">
+        <v>18</v>
+      </c>
+      <c r="L13">
+        <v>30</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14">
+        <v>27</v>
+      </c>
+      <c r="D14">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>0.86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14">
+        <v>570380</v>
+      </c>
+      <c r="I14">
+        <v>27</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>24</v>
+      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="2"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E15">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>570381</v>
+      </c>
+      <c r="I15">
+        <v>29</v>
+      </c>
+      <c r="J15">
+        <v>30</v>
+      </c>
+      <c r="K15">
+        <v>26</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="2"/>
+        <v>0.92666666666666675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16">
+        <v>27</v>
+      </c>
+      <c r="D16">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="E16">
+        <v>0.87333333333333341</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16">
+        <v>570382</v>
+      </c>
+      <c r="I16">
+        <v>27</v>
+      </c>
+      <c r="J16">
+        <v>30</v>
+      </c>
+      <c r="K16">
+        <v>25</v>
+      </c>
+      <c r="L16">
+        <v>30</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="2"/>
+        <v>0.87333333333333341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" t="s">
+        <v>125</v>
+      </c>
+      <c r="L17" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" t="s">
+        <v>125</v>
+      </c>
+      <c r="O17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>0.94</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18">
+        <v>570391</v>
+      </c>
+      <c r="I18">
+        <v>27</v>
+      </c>
+      <c r="J18">
+        <v>30</v>
+      </c>
+      <c r="K18">
+        <v>30</v>
+      </c>
+      <c r="L18">
+        <v>30</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ref="M18:M42" si="3">I18</f>
+        <v>27</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ref="N18:N42" si="4">K18/L18*20</f>
+        <v>20</v>
+      </c>
+      <c r="O18">
+        <f t="shared" ref="O18:O42" si="5">SUM(M18,N18)/50</f>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19">
+        <v>27</v>
+      </c>
+      <c r="D19">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E19">
+        <v>0.88666666666666671</v>
+      </c>
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19">
+        <v>570392</v>
+      </c>
+      <c r="I19">
+        <v>27</v>
+      </c>
+      <c r="J19">
+        <v>30</v>
+      </c>
+      <c r="K19">
+        <v>26</v>
+      </c>
+      <c r="L19">
+        <v>30</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>0.88666666666666671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20">
+        <v>28</v>
+      </c>
+      <c r="D20">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E20">
+        <v>0.90666666666666673</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20">
+        <v>570418</v>
+      </c>
+      <c r="I20">
+        <v>28</v>
+      </c>
+      <c r="J20">
+        <v>30</v>
+      </c>
+      <c r="K20">
+        <v>26</v>
+      </c>
+      <c r="L20">
+        <v>30</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="5"/>
+        <v>0.90666666666666673</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>27</v>
+      </c>
+      <c r="D21">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E21">
+        <v>0.88666666666666671</v>
+      </c>
+      <c r="G21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21">
+        <v>570419</v>
+      </c>
+      <c r="I21">
+        <v>27</v>
+      </c>
+      <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21">
+        <v>26</v>
+      </c>
+      <c r="L21">
+        <v>30</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="5"/>
+        <v>0.88666666666666671</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22">
+        <v>26</v>
+      </c>
+      <c r="D22">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="E22">
+        <v>0.74666666666666659</v>
+      </c>
+      <c r="G22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22">
+        <v>570420</v>
+      </c>
+      <c r="I22">
+        <v>26</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
+      </c>
+      <c r="K22">
+        <v>17</v>
+      </c>
+      <c r="L22">
+        <v>30</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="4"/>
+        <v>11.333333333333332</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="5"/>
+        <v>0.74666666666666659</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23">
+        <v>28</v>
+      </c>
+      <c r="D23">
+        <v>11.333333333333332</v>
+      </c>
+      <c r="E23">
+        <v>0.78666666666666663</v>
+      </c>
+      <c r="G23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23">
+        <v>570421</v>
+      </c>
+      <c r="I23">
+        <v>28</v>
+      </c>
+      <c r="J23">
+        <v>30</v>
+      </c>
+      <c r="K23">
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <v>30</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="4"/>
+        <v>11.333333333333332</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="5"/>
+        <v>0.78666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24">
+        <v>21</v>
+      </c>
+      <c r="D24">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="E24">
+        <v>0.72666666666666668</v>
+      </c>
+      <c r="G24" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24">
+        <v>570423</v>
+      </c>
+      <c r="I24">
+        <v>21</v>
+      </c>
+      <c r="J24">
+        <v>30</v>
+      </c>
+      <c r="K24">
+        <v>23</v>
+      </c>
+      <c r="L24">
+        <v>30</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="4"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="5"/>
+        <v>0.72666666666666668</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="E25">
+        <v>0.89333333333333342</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25">
+        <v>570424</v>
+      </c>
+      <c r="I25">
+        <v>26</v>
+      </c>
+      <c r="J25">
+        <v>30</v>
+      </c>
+      <c r="K25">
+        <v>28</v>
+      </c>
+      <c r="L25">
+        <v>30</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="4"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="5"/>
+        <v>0.89333333333333342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E26">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26">
+        <v>570425</v>
+      </c>
+      <c r="I26">
+        <v>29</v>
+      </c>
+      <c r="J26">
+        <v>30</v>
+      </c>
+      <c r="K26">
+        <v>26</v>
+      </c>
+      <c r="L26">
+        <v>30</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="5"/>
+        <v>0.92666666666666675</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E27">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27">
+        <v>570434</v>
+      </c>
+      <c r="I27">
+        <v>26</v>
+      </c>
+      <c r="J27">
+        <v>30</v>
+      </c>
+      <c r="K27">
+        <v>26</v>
+      </c>
+      <c r="L27">
+        <v>30</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="5"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28">
+        <v>28</v>
+      </c>
+      <c r="D28">
+        <v>20</v>
+      </c>
+      <c r="E28">
+        <v>0.96</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28">
+        <v>570442</v>
+      </c>
+      <c r="I28">
+        <v>28</v>
+      </c>
+      <c r="J28">
+        <v>30</v>
+      </c>
+      <c r="K28">
+        <v>30</v>
+      </c>
+      <c r="L28">
+        <v>30</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="5"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E29">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29">
+        <v>570444</v>
+      </c>
+      <c r="I29">
+        <v>26</v>
+      </c>
+      <c r="J29">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>26</v>
+      </c>
+      <c r="L29">
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="5"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30">
+        <v>27</v>
+      </c>
+      <c r="D30">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="E30">
+        <v>0.91333333333333344</v>
+      </c>
+      <c r="G30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30">
+        <v>570468</v>
+      </c>
+      <c r="I30">
+        <v>27</v>
+      </c>
+      <c r="J30">
+        <v>30</v>
+      </c>
+      <c r="K30">
+        <v>28</v>
+      </c>
+      <c r="L30">
+        <v>30</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="4"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="5"/>
+        <v>0.91333333333333344</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31">
+        <v>24</v>
+      </c>
+      <c r="D31">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="E31">
+        <v>0.78666666666666674</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31">
+        <v>570469</v>
+      </c>
+      <c r="I31">
+        <v>24</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>23</v>
+      </c>
+      <c r="L31">
+        <v>30</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="4"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="5"/>
+        <v>0.78666666666666674</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32">
+        <v>27</v>
+      </c>
+      <c r="D32">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="E32">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="G32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32">
+        <v>570532</v>
+      </c>
+      <c r="I32">
+        <v>27</v>
+      </c>
+      <c r="J32">
+        <v>30</v>
+      </c>
+      <c r="K32">
+        <v>22</v>
+      </c>
+      <c r="L32">
+        <v>30</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="4"/>
+        <v>14.666666666666666</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33">
+        <v>28</v>
+      </c>
+      <c r="D33">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="E33">
+        <v>0.93333333333333346</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33">
+        <v>570534</v>
+      </c>
+      <c r="I33">
+        <v>28</v>
+      </c>
+      <c r="J33">
+        <v>30</v>
+      </c>
+      <c r="K33">
+        <v>28</v>
+      </c>
+      <c r="L33">
+        <v>30</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="4"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="5"/>
+        <v>0.93333333333333346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34">
+        <v>27</v>
+      </c>
+      <c r="D34">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>0.9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34">
+        <v>570535</v>
+      </c>
+      <c r="I34">
+        <v>27</v>
+      </c>
+      <c r="J34">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>27</v>
+      </c>
+      <c r="L34">
+        <v>30</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35">
+        <v>27</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>0.9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35">
+        <v>570536</v>
+      </c>
+      <c r="I35">
+        <v>27</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>27</v>
+      </c>
+      <c r="L35">
+        <v>30</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36">
+        <v>27</v>
+      </c>
+      <c r="D36">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="E36">
+        <v>0.84666666666666668</v>
+      </c>
+      <c r="G36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36">
+        <v>570537</v>
+      </c>
+      <c r="I36">
+        <v>27</v>
+      </c>
+      <c r="J36">
+        <v>30</v>
+      </c>
+      <c r="K36">
+        <v>23</v>
+      </c>
+      <c r="L36">
+        <v>30</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="4"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="5"/>
+        <v>0.84666666666666668</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37">
+        <v>29</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37">
+        <v>0.98</v>
+      </c>
+      <c r="G37" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37">
+        <v>570538</v>
+      </c>
+      <c r="I37">
+        <v>29</v>
+      </c>
+      <c r="J37">
+        <v>30</v>
+      </c>
+      <c r="K37">
+        <v>30</v>
+      </c>
+      <c r="L37">
+        <v>30</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="5"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>6.6666666666666661</v>
+      </c>
+      <c r="E38">
+        <v>0.71333333333333326</v>
+      </c>
+      <c r="G38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <v>570539</v>
+      </c>
+      <c r="I38">
+        <v>29</v>
+      </c>
+      <c r="J38">
+        <v>30</v>
+      </c>
+      <c r="K38">
+        <v>10</v>
+      </c>
+      <c r="L38">
+        <v>30</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="4"/>
+        <v>6.6666666666666661</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="5"/>
+        <v>0.71333333333333326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="E39">
+        <v>0.90666666666666673</v>
+      </c>
+      <c r="G39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39">
+        <v>570615</v>
+      </c>
+      <c r="I39">
+        <v>30</v>
+      </c>
+      <c r="J39">
+        <v>30</v>
+      </c>
+      <c r="K39">
+        <v>23</v>
+      </c>
+      <c r="L39">
+        <v>30</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="4"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="5"/>
+        <v>0.90666666666666673</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40">
+        <v>26</v>
+      </c>
+      <c r="D40">
+        <v>13.333333333333332</v>
+      </c>
+      <c r="E40">
+        <v>0.78666666666666663</v>
+      </c>
+      <c r="G40" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40">
+        <v>570768</v>
+      </c>
+      <c r="I40">
+        <v>26</v>
+      </c>
+      <c r="J40">
+        <v>30</v>
+      </c>
+      <c r="K40">
+        <v>20</v>
+      </c>
+      <c r="L40">
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="4"/>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="5"/>
+        <v>0.78666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41">
+        <v>29</v>
+      </c>
+      <c r="D41">
+        <v>17.333333333333336</v>
+      </c>
+      <c r="E41">
+        <v>0.92666666666666675</v>
+      </c>
+      <c r="G41" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41">
+        <v>570816</v>
+      </c>
+      <c r="I41">
+        <v>29</v>
+      </c>
+      <c r="J41">
+        <v>30</v>
+      </c>
+      <c r="K41">
+        <v>26</v>
+      </c>
+      <c r="L41">
+        <v>30</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="4"/>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="5"/>
+        <v>0.92666666666666675</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42">
+        <v>29</v>
+      </c>
+      <c r="D42">
+        <v>20</v>
+      </c>
+      <c r="E42">
+        <v>0.98</v>
+      </c>
+      <c r="G42" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42">
+        <v>570838</v>
+      </c>
+      <c r="I42">
+        <v>29</v>
+      </c>
+      <c r="J42">
+        <v>30</v>
+      </c>
+      <c r="K42">
+        <v>30</v>
+      </c>
+      <c r="L42">
+        <v>30</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="5"/>
+        <v>0.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A49BB2B-8B42-44D8-881C-CDFBCCFF804F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD3C762-BFDF-4622-B314-C83350713995}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SQL!$B$3:$G$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$B$2:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$B$2:$I$43</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="136">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -444,9 +444,6 @@
   </si>
   <si>
     <t>ReactJs</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1006,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="I6" s="15">
-        <v>0.67333333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1332,8 +1329,8 @@
       <c r="H18" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>136</v>
+      <c r="I18" s="4">
+        <v>0.84</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -1522,7 +1519,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="I25" s="4">
-        <v>0.72666666666666668</v>
+        <v>0.84</v>
       </c>
       <c r="J25" s="3"/>
     </row>
@@ -1711,7 +1708,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="I32" s="4">
-        <v>0.78666666666666674</v>
+        <v>0.92</v>
       </c>
       <c r="J32" s="3"/>
     </row>
@@ -1900,7 +1897,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="I39" s="4">
-        <v>0.71333333333333326</v>
+        <v>0.90666666666666673</v>
       </c>
       <c r="J39" s="3"/>
     </row>
@@ -7915,7 +7912,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{379B70B4-E4BA-416C-BDA9-CDEC7B2C6BC8}">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -8125,13 +8122,13 @@
         <v>71</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>9.3333333333333339</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>0.67333333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="G5" t="s">
         <v>94</v>
@@ -8688,14 +8685,14 @@
       <c r="B17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>125</v>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>0.84</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>68</v>
@@ -8768,7 +8765,7 @@
         <v>20</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O42" si="5">SUM(M18,N18)/50</f>
+        <f t="shared" ref="O18:O43" si="5">SUM(M18,N18)/50</f>
         <v>0.94</v>
       </c>
     </row>
@@ -9015,13 +9012,13 @@
         <v>54</v>
       </c>
       <c r="C24">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D24">
-        <v>15.333333333333334</v>
+        <v>16</v>
       </c>
       <c r="E24">
-        <v>0.72666666666666668</v>
+        <v>0.84</v>
       </c>
       <c r="G24" t="s">
         <v>54</v>
@@ -9344,13 +9341,13 @@
         <v>63</v>
       </c>
       <c r="C31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D31">
-        <v>15.333333333333334</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>0.78666666666666674</v>
+        <v>0.92</v>
       </c>
       <c r="G31" t="s">
         <v>63</v>
@@ -9673,13 +9670,13 @@
         <v>60</v>
       </c>
       <c r="C38">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38">
-        <v>6.6666666666666661</v>
+        <v>17.333333333333336</v>
       </c>
       <c r="E38">
-        <v>0.71333333333333326</v>
+        <v>0.90666666666666673</v>
       </c>
       <c r="G38" t="s">
         <v>60</v>
@@ -9898,6 +9895,166 @@
       <c r="O42">
         <f t="shared" si="5"/>
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43">
+        <v>570390</v>
+      </c>
+      <c r="I43">
+        <v>26</v>
+      </c>
+      <c r="J43">
+        <v>30</v>
+      </c>
+      <c r="K43">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>30</v>
+      </c>
+      <c r="M43">
+        <f>I43</f>
+        <v>26</v>
+      </c>
+      <c r="N43">
+        <f>K43/L43*20</f>
+        <v>16</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="5"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G44" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44">
+        <v>570539</v>
+      </c>
+      <c r="I44">
+        <v>28</v>
+      </c>
+      <c r="J44">
+        <v>30</v>
+      </c>
+      <c r="K44">
+        <v>26</v>
+      </c>
+      <c r="L44">
+        <v>30</v>
+      </c>
+      <c r="M44">
+        <f t="shared" ref="M44:M47" si="6">I44</f>
+        <v>28</v>
+      </c>
+      <c r="N44">
+        <f>K44/L44*20</f>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="O44">
+        <f>SUM(M44:N44)/50</f>
+        <v>0.90666666666666673</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G45" t="s">
+        <v>63</v>
+      </c>
+      <c r="H45">
+        <v>570469</v>
+      </c>
+      <c r="I45">
+        <v>28</v>
+      </c>
+      <c r="J45">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>27</v>
+      </c>
+      <c r="L45">
+        <v>30</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="N45">
+        <f t="shared" ref="N45:N47" si="7">K45/L45*20</f>
+        <v>18</v>
+      </c>
+      <c r="O45">
+        <f t="shared" ref="O45:O47" si="8">SUM(M45:N45)/50</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46">
+        <v>570363</v>
+      </c>
+      <c r="I46">
+        <v>28</v>
+      </c>
+      <c r="J46">
+        <v>30</v>
+      </c>
+      <c r="K46">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>30</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="8"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G47" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47">
+        <v>570423</v>
+      </c>
+      <c r="I47">
+        <v>26</v>
+      </c>
+      <c r="J47">
+        <v>30</v>
+      </c>
+      <c r="K47">
+        <v>24</v>
+      </c>
+      <c r="L47">
+        <v>30</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="8"/>
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>

--- a/Assessments/Scores.xlsx
+++ b/Assessments/Scores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD3C762-BFDF-4622-B314-C83350713995}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2878DD1-BDC4-4EB6-AFBB-C3EF1071562C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2F9F5002-5604-4D98-B7B9-A4CE7BA2379C}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Spring" sheetId="5" r:id="rId5"/>
     <sheet name="HTML_CSS_Js" sheetId="6" r:id="rId6"/>
     <sheet name="ReactJs" sheetId="7" r:id="rId7"/>
+    <sheet name="FinalTest" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PLSQL!$B$2:$G$41</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="140">
   <si>
     <t>Employee Id:</t>
   </si>
@@ -444,6 +445,18 @@
   </si>
   <si>
     <t>ReactJs</t>
+  </si>
+  <si>
+    <t>Final Test</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>Rupesh</t>
+  </si>
+  <si>
+    <t>Hari Prasad</t>
   </si>
 </sst>
 </file>
@@ -530,7 +543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -548,7 +561,6 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,7 +884,7 @@
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="6.88671875" customWidth="1"/>
-    <col min="10" max="10" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -900,7 +912,9 @@
       <c r="I2" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="5" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -927,7 +941,9 @@
       <c r="I3" s="4">
         <v>0.80666666666666653</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -954,7 +970,9 @@
       <c r="I4" s="4">
         <v>0.84</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -981,7 +999,9 @@
       <c r="I5" s="4">
         <v>0.87333333333333329</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
@@ -1005,10 +1025,12 @@
       <c r="H6" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="4">
         <v>0.88</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
@@ -1035,7 +1057,9 @@
       <c r="I7" s="4">
         <v>0.94</v>
       </c>
-      <c r="J7" s="3"/>
+      <c r="J7" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -1062,7 +1086,9 @@
       <c r="I8" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -1089,7 +1115,9 @@
       <c r="I9" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="J9" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1116,7 +1144,9 @@
       <c r="I10" s="4">
         <v>0.9</v>
       </c>
-      <c r="J10" s="3"/>
+      <c r="J10" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -1143,7 +1173,9 @@
       <c r="I11" s="4">
         <v>0.84</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -1170,7 +1202,9 @@
       <c r="I12" s="4">
         <v>0.81333333333333324</v>
       </c>
-      <c r="J12" s="3"/>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -1197,7 +1231,9 @@
       <c r="I13" s="4">
         <v>0.94666666666666655</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
@@ -1224,7 +1260,9 @@
       <c r="I14" s="4">
         <v>0.8</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
@@ -1251,7 +1289,9 @@
       <c r="I15" s="4">
         <v>0.86</v>
       </c>
-      <c r="J15" s="3"/>
+      <c r="J15" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
@@ -1278,7 +1318,9 @@
       <c r="I16" s="4">
         <v>0.92666666666666675</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
@@ -1305,7 +1347,9 @@
       <c r="I17" s="4">
         <v>0.87333333333333341</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
@@ -1332,7 +1376,9 @@
       <c r="I18" s="4">
         <v>0.84</v>
       </c>
-      <c r="J18" s="3"/>
+      <c r="J18" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
@@ -1359,7 +1405,9 @@
       <c r="I19" s="4">
         <v>0.94</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
@@ -1386,7 +1434,9 @@
       <c r="I20" s="4">
         <v>0.88666666666666671</v>
       </c>
-      <c r="J20" s="3"/>
+      <c r="J20" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
@@ -1413,7 +1463,9 @@
       <c r="I21" s="4">
         <v>0.90666666666666673</v>
       </c>
-      <c r="J21" s="3"/>
+      <c r="J21" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
@@ -1440,7 +1492,9 @@
       <c r="I22" s="4">
         <v>0.88666666666666671</v>
       </c>
-      <c r="J22" s="3"/>
+      <c r="J22" s="4">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
@@ -1467,7 +1521,9 @@
       <c r="I23" s="4">
         <v>0.74666666666666659</v>
       </c>
-      <c r="J23" s="3"/>
+      <c r="J23" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
@@ -1494,7 +1550,9 @@
       <c r="I24" s="4">
         <v>0.78666666666666663</v>
       </c>
-      <c r="J24" s="3"/>
+      <c r="J24" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
@@ -1521,7 +1579,9 @@
       <c r="I25" s="4">
         <v>0.84</v>
       </c>
-      <c r="J25" s="3"/>
+      <c r="J25" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
@@ -1548,7 +1608,9 @@
       <c r="I26" s="4">
         <v>0.89333333333333342</v>
       </c>
-      <c r="J26" s="3"/>
+      <c r="J26" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
@@ -1575,7 +1637,9 @@
       <c r="I27" s="4">
         <v>0.92666666666666675</v>
       </c>
-      <c r="J27" s="3"/>
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
@@ -1602,7 +1666,9 @@
       <c r="I28" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J28" s="3"/>
+      <c r="J28" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
@@ -1629,7 +1695,9 @@
       <c r="I29" s="4">
         <v>0.96</v>
       </c>
-      <c r="J29" s="3"/>
+      <c r="J29" s="4">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
@@ -1656,7 +1724,9 @@
       <c r="I30" s="4">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J30" s="3"/>
+      <c r="J30" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
@@ -1683,7 +1753,9 @@
       <c r="I31" s="4">
         <v>0.91333333333333344</v>
       </c>
-      <c r="J31" s="3"/>
+      <c r="J31" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
@@ -1710,7 +1782,9 @@
       <c r="I32" s="4">
         <v>0.92</v>
       </c>
-      <c r="J32" s="3"/>
+      <c r="J32" s="4">
+        <v>0.94</v>
+      </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
@@ -1737,7 +1811,9 @@
       <c r="I33" s="4">
         <v>0.83333333333333326</v>
       </c>
-      <c r="J33" s="3"/>
+      <c r="J33" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
@@ -1764,7 +1840,9 @@
       <c r="I34" s="4">
         <v>0.93333333333333346</v>
       </c>
-      <c r="J34" s="3"/>
+      <c r="J34" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
@@ -1791,7 +1869,9 @@
       <c r="I35" s="4">
         <v>0.9</v>
       </c>
-      <c r="J35" s="3"/>
+      <c r="J35" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
@@ -1818,7 +1898,9 @@
       <c r="I36" s="4">
         <v>0.9</v>
       </c>
-      <c r="J36" s="3"/>
+      <c r="J36" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
@@ -1845,7 +1927,9 @@
       <c r="I37" s="4">
         <v>0.84666666666666668</v>
       </c>
-      <c r="J37" s="3"/>
+      <c r="J37" s="4">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
@@ -1872,7 +1956,9 @@
       <c r="I38" s="4">
         <v>0.98</v>
       </c>
-      <c r="J38" s="3"/>
+      <c r="J38" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
@@ -1899,7 +1985,9 @@
       <c r="I39" s="4">
         <v>0.90666666666666673</v>
       </c>
-      <c r="J39" s="3"/>
+      <c r="J39" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
@@ -1926,7 +2014,9 @@
       <c r="I40" s="4">
         <v>0.90666666666666673</v>
       </c>
-      <c r="J40" s="3"/>
+      <c r="J40" s="4">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
@@ -1953,7 +2043,9 @@
       <c r="I41" s="4">
         <v>0.78666666666666663</v>
       </c>
-      <c r="J41" s="3"/>
+      <c r="J41" s="4">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
@@ -1980,7 +2072,9 @@
       <c r="I42" s="4">
         <v>0.92666666666666675</v>
       </c>
-      <c r="J42" s="3"/>
+      <c r="J42" s="4">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
@@ -2007,7 +2101,9 @@
       <c r="I43" s="4">
         <v>0.98</v>
       </c>
-      <c r="J43" s="3"/>
+      <c r="J43" s="4">
+        <v>0.98</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10060,4 +10156,1284 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF436225-F617-49CE-8371-EE91BB64450B}">
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="12">
+        <v>45923.469247685185</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I42" si="0">D2/E2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="12">
+        <v>45923.473287037035</v>
+      </c>
+      <c r="D3">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4">
+        <v>570362</v>
+      </c>
+      <c r="C4" s="12">
+        <v>45923.469618055555</v>
+      </c>
+      <c r="D4">
+        <v>48</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5">
+        <v>570363</v>
+      </c>
+      <c r="C5" s="12">
+        <v>45923.47079861111</v>
+      </c>
+      <c r="D5">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6">
+        <v>570365</v>
+      </c>
+      <c r="C6" s="12">
+        <v>45923.474768518521</v>
+      </c>
+      <c r="D6">
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7">
+        <v>570367</v>
+      </c>
+      <c r="C7" s="12">
+        <v>45923.470185185186</v>
+      </c>
+      <c r="D7">
+        <v>49</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8">
+        <v>570371</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45923.465798611112</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9">
+        <v>570372</v>
+      </c>
+      <c r="C9" s="12">
+        <v>45923.47042824074</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10">
+        <v>570373</v>
+      </c>
+      <c r="C10" s="12">
+        <v>45923.463692129626</v>
+      </c>
+      <c r="D10">
+        <v>47</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>570375</v>
+      </c>
+      <c r="C11" s="12">
+        <v>45923.471759259257</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12">
+        <v>570376</v>
+      </c>
+      <c r="C12" s="12">
+        <v>45923.470613425925</v>
+      </c>
+      <c r="D12">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13">
+        <v>570377</v>
+      </c>
+      <c r="C13" s="12">
+        <v>45923.471967592595</v>
+      </c>
+      <c r="D13">
+        <v>48</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14">
+        <v>570380</v>
+      </c>
+      <c r="C14" s="12">
+        <v>45923.465798611112</v>
+      </c>
+      <c r="D14">
+        <v>47</v>
+      </c>
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>570381</v>
+      </c>
+      <c r="C15" s="12">
+        <v>45923.466099537036</v>
+      </c>
+      <c r="D15">
+        <v>49</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>570382</v>
+      </c>
+      <c r="C16" s="12">
+        <v>45923.463090277779</v>
+      </c>
+      <c r="D16">
+        <v>47</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17">
+        <v>570390</v>
+      </c>
+      <c r="C17" s="12">
+        <v>45923.466099537036</v>
+      </c>
+      <c r="D17">
+        <v>49</v>
+      </c>
+      <c r="E17">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18">
+        <v>570391</v>
+      </c>
+      <c r="C18" s="12">
+        <v>45923.475289351853</v>
+      </c>
+      <c r="D18">
+        <v>48</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19">
+        <v>570392</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45923.475891203707</v>
+      </c>
+      <c r="D19">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>570418</v>
+      </c>
+      <c r="C20" s="12">
+        <v>45923.470219907409</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21">
+        <v>570419</v>
+      </c>
+      <c r="C21" s="12">
+        <v>45923.467777777776</v>
+      </c>
+      <c r="D21">
+        <v>46</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22">
+        <v>570420</v>
+      </c>
+      <c r="C22" s="12">
+        <v>45923.469872685186</v>
+      </c>
+      <c r="D22">
+        <v>47</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23">
+        <v>570421</v>
+      </c>
+      <c r="C23" s="12">
+        <v>45923.471388888887</v>
+      </c>
+      <c r="D23">
+        <v>49</v>
+      </c>
+      <c r="E23">
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24">
+        <v>570423</v>
+      </c>
+      <c r="C24" s="12">
+        <v>45923.474976851852</v>
+      </c>
+      <c r="D24">
+        <v>48</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>570424</v>
+      </c>
+      <c r="C25" s="12">
+        <v>45923.470451388886</v>
+      </c>
+      <c r="D25">
+        <v>49</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26">
+        <v>570425</v>
+      </c>
+      <c r="C26" s="12">
+        <v>45923.467314814814</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+      <c r="E26">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27">
+        <v>570434</v>
+      </c>
+      <c r="C27" s="12">
+        <v>45923.473981481482</v>
+      </c>
+      <c r="D27">
+        <v>49</v>
+      </c>
+      <c r="E27">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>120</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28">
+        <v>570442</v>
+      </c>
+      <c r="C28" s="12">
+        <v>45923.475104166668</v>
+      </c>
+      <c r="D28">
+        <v>45</v>
+      </c>
+      <c r="E28">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>120</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29">
+        <v>570444</v>
+      </c>
+      <c r="C29" s="12">
+        <v>45923.465752314813</v>
+      </c>
+      <c r="D29">
+        <v>48</v>
+      </c>
+      <c r="E29">
+        <v>50</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30">
+        <v>570468</v>
+      </c>
+      <c r="C30" s="12">
+        <v>45923.473333333335</v>
+      </c>
+      <c r="D30">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>50</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31">
+        <v>570469</v>
+      </c>
+      <c r="C31" s="12">
+        <v>45923.471087962964</v>
+      </c>
+      <c r="D31">
+        <v>47</v>
+      </c>
+      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32">
+        <v>570532</v>
+      </c>
+      <c r="C32" s="12">
+        <v>45923.472222222219</v>
+      </c>
+      <c r="D32">
+        <v>49</v>
+      </c>
+      <c r="E32">
+        <v>50</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>120</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33">
+        <v>570534</v>
+      </c>
+      <c r="C33" s="12">
+        <v>45923.46806712963</v>
+      </c>
+      <c r="D33">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>120</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34">
+        <v>570535</v>
+      </c>
+      <c r="C34" s="12">
+        <v>45923.466145833336</v>
+      </c>
+      <c r="D34">
+        <v>49</v>
+      </c>
+      <c r="E34">
+        <v>50</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35">
+        <v>570536</v>
+      </c>
+      <c r="C35" s="12">
+        <v>45923.470729166664</v>
+      </c>
+      <c r="D35">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36">
+        <v>570537</v>
+      </c>
+      <c r="C36" s="12">
+        <v>45923.468460648146</v>
+      </c>
+      <c r="D36">
+        <v>46</v>
+      </c>
+      <c r="E36">
+        <v>50</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37">
+        <v>570538</v>
+      </c>
+      <c r="C37" s="12">
+        <v>45923.465624999997</v>
+      </c>
+      <c r="D37">
+        <v>50</v>
+      </c>
+      <c r="E37">
+        <v>50</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>120</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38">
+        <v>570539</v>
+      </c>
+      <c r="C38" s="12">
+        <v>45923.470879629633</v>
+      </c>
+      <c r="D38">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>50</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>120</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39">
+        <v>570615</v>
+      </c>
+      <c r="C39" s="12">
+        <v>45923.467893518522</v>
+      </c>
+      <c r="D39">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>50</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40">
+        <v>570768</v>
+      </c>
+      <c r="C40" s="12">
+        <v>45923.470219907409</v>
+      </c>
+      <c r="D40">
+        <v>46</v>
+      </c>
+      <c r="E40">
+        <v>50</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>120</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41">
+        <v>570816</v>
+      </c>
+      <c r="C41" s="12">
+        <v>45923.46675925926</v>
+      </c>
+      <c r="D41">
+        <v>49</v>
+      </c>
+      <c r="E41">
+        <v>50</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42">
+        <v>570838</v>
+      </c>
+      <c r="C42" s="12">
+        <v>45923.471898148149</v>
+      </c>
+      <c r="D42">
+        <v>49</v>
+      </c>
+      <c r="E42">
+        <v>50</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>0.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>